--- a/Sample dataxlsx.xlsx
+++ b/Sample dataxlsx.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\S2 Smart Manufacturing and Applied information science\2 Semester\Advance Statistical Quality Control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E27B0D6E-79D4-41D8-A4BE-B1C232AD20EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A8B4AD-8B50-4534-87AA-F0F9DCCAC02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="1" xr2:uid="{E9B4DBE7-7145-4880-9E7C-D6384306006F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{E9B4DBE7-7145-4880-9E7C-D6384306006F}"/>
   </bookViews>
   <sheets>
     <sheet name="CUSUM Chart" sheetId="3" r:id="rId1"/>
     <sheet name="xbar " sheetId="1" r:id="rId2"/>
     <sheet name="MR Chart" sheetId="4" r:id="rId3"/>
+    <sheet name="pchart" sheetId="8" r:id="rId4"/>
+    <sheet name="np chart" sheetId="9" r:id="rId5"/>
+    <sheet name="cchart" sheetId="10" r:id="rId6"/>
+    <sheet name="uchart" sheetId="11" r:id="rId7"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="68">
   <si>
     <t>G1</t>
   </si>
@@ -225,16 +226,62 @@
   <si>
     <t>On the MR 39th have data higher than UCL</t>
   </si>
+  <si>
+    <t>Sample Number</t>
+  </si>
+  <si>
+    <t>Number of Nonconforming Cans (Di​)</t>
+  </si>
+  <si>
+    <t>Sample Fraction Nonconforming (p^​i​)</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Sample Fraction Nonconforming (pi​)</t>
+  </si>
+  <si>
+    <t>Sample Number (i)</t>
+  </si>
+  <si>
+    <t>Sample Size (ni​)</t>
+  </si>
+  <si>
+    <t>Number of Nonconforming Units (Di​)</t>
+  </si>
+  <si>
+    <t>Fraction Nonconforming (pi​)</t>
+  </si>
+  <si>
+    <t>pbar</t>
+  </si>
+  <si>
+    <t>Number of Nonconformities</t>
+  </si>
+  <si>
+    <t>Unit Inspeksi (ni​)</t>
+  </si>
+  <si>
+    <t>Jumlah Cacat (ci​)</t>
+  </si>
+  <si>
+    <t>Rata-rata Cacat per Unit (ui​=ci​/ni​)</t>
+  </si>
+  <si>
+    <t>std dev</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -259,6 +306,19 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -288,7 +348,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -363,11 +423,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -404,20 +490,42 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7593,1306 +7701,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="MR Chart"/>
-      <sheetName val="CUSUM Chart"/>
-      <sheetName val="Sheet3"/>
-      <sheetName val="Sheet2"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="B2">
-            <v>310</v>
-          </cell>
-          <cell r="D2">
-            <v>300.5</v>
-          </cell>
-          <cell r="E2">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F2">
-            <v>279.78331466965284</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>288</v>
-          </cell>
-          <cell r="D3">
-            <v>300.5</v>
-          </cell>
-          <cell r="E3">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F3">
-            <v>279.78331466965284</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4">
-            <v>297</v>
-          </cell>
-          <cell r="D4">
-            <v>300.5</v>
-          </cell>
-          <cell r="E4">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F4">
-            <v>279.78331466965284</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5">
-            <v>298</v>
-          </cell>
-          <cell r="D5">
-            <v>300.5</v>
-          </cell>
-          <cell r="E5">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F5">
-            <v>279.78331466965284</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6">
-            <v>307</v>
-          </cell>
-          <cell r="D6">
-            <v>300.5</v>
-          </cell>
-          <cell r="E6">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F6">
-            <v>279.78331466965284</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7">
-            <v>303</v>
-          </cell>
-          <cell r="D7">
-            <v>300.5</v>
-          </cell>
-          <cell r="E7">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F7">
-            <v>279.78331466965284</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8">
-            <v>294</v>
-          </cell>
-          <cell r="D8">
-            <v>300.5</v>
-          </cell>
-          <cell r="E8">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F8">
-            <v>279.78331466965284</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9">
-            <v>297</v>
-          </cell>
-          <cell r="D9">
-            <v>300.5</v>
-          </cell>
-          <cell r="E9">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F9">
-            <v>279.78331466965284</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10">
-            <v>308</v>
-          </cell>
-          <cell r="D10">
-            <v>300.5</v>
-          </cell>
-          <cell r="E10">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F10">
-            <v>279.78331466965284</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11">
-            <v>306</v>
-          </cell>
-          <cell r="D11">
-            <v>300.5</v>
-          </cell>
-          <cell r="E11">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F11">
-            <v>279.78331466965284</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12">
-            <v>294</v>
-          </cell>
-          <cell r="D12">
-            <v>300.5</v>
-          </cell>
-          <cell r="E12">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F12">
-            <v>279.78331466965284</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13">
-            <v>299</v>
-          </cell>
-          <cell r="D13">
-            <v>300.5</v>
-          </cell>
-          <cell r="E13">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F13">
-            <v>279.78331466965284</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14">
-            <v>297</v>
-          </cell>
-          <cell r="D14">
-            <v>300.5</v>
-          </cell>
-          <cell r="E14">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F14">
-            <v>279.78331466965284</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15">
-            <v>299</v>
-          </cell>
-          <cell r="D15">
-            <v>300.5</v>
-          </cell>
-          <cell r="E15">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F15">
-            <v>279.78331466965284</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16">
-            <v>314</v>
-          </cell>
-          <cell r="D16">
-            <v>300.5</v>
-          </cell>
-          <cell r="E16">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F16">
-            <v>279.78331466965284</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17">
-            <v>295</v>
-          </cell>
-          <cell r="D17">
-            <v>300.5</v>
-          </cell>
-          <cell r="E17">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F17">
-            <v>279.78331466965284</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18">
-            <v>293</v>
-          </cell>
-          <cell r="D18">
-            <v>300.5</v>
-          </cell>
-          <cell r="E18">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F18">
-            <v>279.78331466965284</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="B19">
-            <v>306</v>
-          </cell>
-          <cell r="D19">
-            <v>300.5</v>
-          </cell>
-          <cell r="E19">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F19">
-            <v>279.78331466965284</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20">
-            <v>301</v>
-          </cell>
-          <cell r="D20">
-            <v>300.5</v>
-          </cell>
-          <cell r="E20">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F20">
-            <v>279.78331466965284</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21">
-            <v>304</v>
-          </cell>
-          <cell r="D21">
-            <v>300.5</v>
-          </cell>
-          <cell r="E21">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F21">
-            <v>279.78331466965284</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="D30">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="E30">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="F30">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="C31">
-            <v>22</v>
-          </cell>
-          <cell r="D31">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="E31">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="F31">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="C32">
-            <v>9</v>
-          </cell>
-          <cell r="D32">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="E32">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="F32">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="C33">
-            <v>1</v>
-          </cell>
-          <cell r="D33">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="E33">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="F33">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="C34">
-            <v>9</v>
-          </cell>
-          <cell r="D34">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="E34">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="F34">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="C35">
-            <v>4</v>
-          </cell>
-          <cell r="D35">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="E35">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="F35">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="C36">
-            <v>9</v>
-          </cell>
-          <cell r="D36">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="E36">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="F36">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="C37">
-            <v>3</v>
-          </cell>
-          <cell r="D37">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="E37">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="F37">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="C38">
-            <v>11</v>
-          </cell>
-          <cell r="D38">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="E38">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="F38">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="C39">
-            <v>2</v>
-          </cell>
-          <cell r="D39">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="E39">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="F39">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="C40">
-            <v>12</v>
-          </cell>
-          <cell r="D40">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="E40">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="F40">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="C41">
-            <v>5</v>
-          </cell>
-          <cell r="D41">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="E41">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="F41">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="C42">
-            <v>2</v>
-          </cell>
-          <cell r="D42">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="E42">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="F42">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="C43">
-            <v>2</v>
-          </cell>
-          <cell r="D43">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="E43">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="F43">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="C44">
-            <v>15</v>
-          </cell>
-          <cell r="D44">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="E44">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="F44">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="C45">
-            <v>19</v>
-          </cell>
-          <cell r="D45">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="E45">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="F45">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="C46">
-            <v>2</v>
-          </cell>
-          <cell r="D46">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="E46">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="F46">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="C47">
-            <v>13</v>
-          </cell>
-          <cell r="D47">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="E47">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="F47">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="C48">
-            <v>5</v>
-          </cell>
-          <cell r="D48">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="E48">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="F48">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="C49">
-            <v>3</v>
-          </cell>
-          <cell r="D49">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="E49">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="F49">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="A58">
-            <v>21</v>
-          </cell>
-          <cell r="B58">
-            <v>305</v>
-          </cell>
-          <cell r="D58">
-            <v>300.5</v>
-          </cell>
-          <cell r="E58">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F58">
-            <v>279.78331466965284</v>
-          </cell>
-          <cell r="G58">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="H58">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="I58">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="A59">
-            <v>22</v>
-          </cell>
-          <cell r="B59">
-            <v>282</v>
-          </cell>
-          <cell r="C59">
-            <v>23</v>
-          </cell>
-          <cell r="D59">
-            <v>300.5</v>
-          </cell>
-          <cell r="E59">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F59">
-            <v>279.78331466965284</v>
-          </cell>
-          <cell r="G59">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="H59">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="I59">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="A60">
-            <v>23</v>
-          </cell>
-          <cell r="B60">
-            <v>305</v>
-          </cell>
-          <cell r="C60">
-            <v>23</v>
-          </cell>
-          <cell r="D60">
-            <v>300.5</v>
-          </cell>
-          <cell r="E60">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F60">
-            <v>279.78331466965284</v>
-          </cell>
-          <cell r="G60">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="H60">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="I60">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="A61">
-            <v>24</v>
-          </cell>
-          <cell r="B61">
-            <v>296</v>
-          </cell>
-          <cell r="C61">
-            <v>9</v>
-          </cell>
-          <cell r="D61">
-            <v>300.5</v>
-          </cell>
-          <cell r="E61">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F61">
-            <v>279.78331466965284</v>
-          </cell>
-          <cell r="G61">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="H61">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="I61">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="A62">
-            <v>25</v>
-          </cell>
-          <cell r="B62">
-            <v>314</v>
-          </cell>
-          <cell r="C62">
-            <v>18</v>
-          </cell>
-          <cell r="D62">
-            <v>300.5</v>
-          </cell>
-          <cell r="E62">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F62">
-            <v>279.78331466965284</v>
-          </cell>
-          <cell r="G62">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="H62">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="I62">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="A63">
-            <v>26</v>
-          </cell>
-          <cell r="B63">
-            <v>295</v>
-          </cell>
-          <cell r="C63">
-            <v>19</v>
-          </cell>
-          <cell r="D63">
-            <v>300.5</v>
-          </cell>
-          <cell r="E63">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F63">
-            <v>279.78331466965284</v>
-          </cell>
-          <cell r="G63">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="H63">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="I63">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="A64">
-            <v>27</v>
-          </cell>
-          <cell r="B64">
-            <v>287</v>
-          </cell>
-          <cell r="C64">
-            <v>8</v>
-          </cell>
-          <cell r="D64">
-            <v>300.5</v>
-          </cell>
-          <cell r="E64">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F64">
-            <v>279.78331466965284</v>
-          </cell>
-          <cell r="G64">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="H64">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="I64">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="A65">
-            <v>28</v>
-          </cell>
-          <cell r="B65">
-            <v>301</v>
-          </cell>
-          <cell r="C65">
-            <v>14</v>
-          </cell>
-          <cell r="D65">
-            <v>300.5</v>
-          </cell>
-          <cell r="E65">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F65">
-            <v>279.78331466965284</v>
-          </cell>
-          <cell r="G65">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="H65">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="I65">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="A66">
-            <v>29</v>
-          </cell>
-          <cell r="B66">
-            <v>298</v>
-          </cell>
-          <cell r="C66">
-            <v>3</v>
-          </cell>
-          <cell r="D66">
-            <v>300.5</v>
-          </cell>
-          <cell r="E66">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F66">
-            <v>279.78331466965284</v>
-          </cell>
-          <cell r="G66">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="H66">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="I66">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="A67">
-            <v>30</v>
-          </cell>
-          <cell r="B67">
-            <v>311</v>
-          </cell>
-          <cell r="C67">
-            <v>13</v>
-          </cell>
-          <cell r="D67">
-            <v>300.5</v>
-          </cell>
-          <cell r="E67">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F67">
-            <v>279.78331466965284</v>
-          </cell>
-          <cell r="G67">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="H67">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="I67">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="A68">
-            <v>31</v>
-          </cell>
-          <cell r="B68">
-            <v>310</v>
-          </cell>
-          <cell r="C68">
-            <v>1</v>
-          </cell>
-          <cell r="D68">
-            <v>300.5</v>
-          </cell>
-          <cell r="E68">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F68">
-            <v>279.78331466965284</v>
-          </cell>
-          <cell r="G68">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="H68">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="I68">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="A69">
-            <v>32</v>
-          </cell>
-          <cell r="B69">
-            <v>292</v>
-          </cell>
-          <cell r="C69">
-            <v>18</v>
-          </cell>
-          <cell r="D69">
-            <v>300.5</v>
-          </cell>
-          <cell r="E69">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F69">
-            <v>279.78331466965284</v>
-          </cell>
-          <cell r="G69">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="H69">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="I69">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="A70">
-            <v>33</v>
-          </cell>
-          <cell r="B70">
-            <v>305</v>
-          </cell>
-          <cell r="C70">
-            <v>13</v>
-          </cell>
-          <cell r="D70">
-            <v>300.5</v>
-          </cell>
-          <cell r="E70">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F70">
-            <v>279.78331466965284</v>
-          </cell>
-          <cell r="G70">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="H70">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="I70">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="A71">
-            <v>34</v>
-          </cell>
-          <cell r="B71">
-            <v>299</v>
-          </cell>
-          <cell r="C71">
-            <v>6</v>
-          </cell>
-          <cell r="D71">
-            <v>300.5</v>
-          </cell>
-          <cell r="E71">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F71">
-            <v>279.78331466965284</v>
-          </cell>
-          <cell r="G71">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="H71">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="I71">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="A72">
-            <v>35</v>
-          </cell>
-          <cell r="B72">
-            <v>304</v>
-          </cell>
-          <cell r="C72">
-            <v>5</v>
-          </cell>
-          <cell r="D72">
-            <v>300.5</v>
-          </cell>
-          <cell r="E72">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F72">
-            <v>279.78331466965284</v>
-          </cell>
-          <cell r="G72">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="H72">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="I72">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="A73">
-            <v>36</v>
-          </cell>
-          <cell r="B73">
-            <v>310</v>
-          </cell>
-          <cell r="C73">
-            <v>6</v>
-          </cell>
-          <cell r="D73">
-            <v>300.5</v>
-          </cell>
-          <cell r="E73">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F73">
-            <v>279.78331466965284</v>
-          </cell>
-          <cell r="G73">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="H73">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="I73">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="A74">
-            <v>37</v>
-          </cell>
-          <cell r="B74">
-            <v>304</v>
-          </cell>
-          <cell r="C74">
-            <v>6</v>
-          </cell>
-          <cell r="D74">
-            <v>300.5</v>
-          </cell>
-          <cell r="E74">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F74">
-            <v>279.78331466965284</v>
-          </cell>
-          <cell r="G74">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="H74">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="I74">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="A75">
-            <v>38</v>
-          </cell>
-          <cell r="B75">
-            <v>305</v>
-          </cell>
-          <cell r="C75">
-            <v>1</v>
-          </cell>
-          <cell r="D75">
-            <v>300.5</v>
-          </cell>
-          <cell r="E75">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F75">
-            <v>279.78331466965284</v>
-          </cell>
-          <cell r="G75">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="H75">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="I75">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="A76">
-            <v>39</v>
-          </cell>
-          <cell r="B76">
-            <v>333</v>
-          </cell>
-          <cell r="C76">
-            <v>28</v>
-          </cell>
-          <cell r="D76">
-            <v>300.5</v>
-          </cell>
-          <cell r="E76">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F76">
-            <v>279.78331466965284</v>
-          </cell>
-          <cell r="G76">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="H76">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="I76">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="A77">
-            <v>40</v>
-          </cell>
-          <cell r="B77">
-            <v>328</v>
-          </cell>
-          <cell r="C77">
-            <v>5</v>
-          </cell>
-          <cell r="D77">
-            <v>300.5</v>
-          </cell>
-          <cell r="E77">
-            <v>321.21668533034716</v>
-          </cell>
-          <cell r="F77">
-            <v>279.78331466965284</v>
-          </cell>
-          <cell r="G77">
-            <v>7.7894736842105265</v>
-          </cell>
-          <cell r="H77">
-            <v>25.448210526315791</v>
-          </cell>
-          <cell r="I77">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="C2">
-            <v>0</v>
-          </cell>
-          <cell r="D2">
-            <v>0</v>
-          </cell>
-          <cell r="E2">
-            <v>-5</v>
-          </cell>
-          <cell r="F2">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="C3">
-            <v>0</v>
-          </cell>
-          <cell r="D3">
-            <v>0</v>
-          </cell>
-          <cell r="E3">
-            <v>-5</v>
-          </cell>
-          <cell r="F3">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="C4">
-            <v>0.10000000000000142</v>
-          </cell>
-          <cell r="D4">
-            <v>0</v>
-          </cell>
-          <cell r="E4">
-            <v>-5</v>
-          </cell>
-          <cell r="F4">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="C5">
-            <v>0.60000000000000142</v>
-          </cell>
-          <cell r="D5">
-            <v>0</v>
-          </cell>
-          <cell r="E5">
-            <v>-5</v>
-          </cell>
-          <cell r="F5">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="C6">
-            <v>1.3000000000000043</v>
-          </cell>
-          <cell r="D6">
-            <v>0</v>
-          </cell>
-          <cell r="E6">
-            <v>-5</v>
-          </cell>
-          <cell r="F6">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="C7">
-            <v>2.3000000000000043</v>
-          </cell>
-          <cell r="D7">
-            <v>0</v>
-          </cell>
-          <cell r="E7">
-            <v>-5</v>
-          </cell>
-          <cell r="F7">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="C8">
-            <v>3.2000000000000028</v>
-          </cell>
-          <cell r="D8">
-            <v>0</v>
-          </cell>
-          <cell r="E8">
-            <v>-5</v>
-          </cell>
-          <cell r="F8">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="C9">
-            <v>4</v>
-          </cell>
-          <cell r="D9">
-            <v>0</v>
-          </cell>
-          <cell r="E9">
-            <v>-5</v>
-          </cell>
-          <cell r="F9">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="C10">
-            <v>5.1000000000000014</v>
-          </cell>
-          <cell r="D10">
-            <v>0</v>
-          </cell>
-          <cell r="E10">
-            <v>-5</v>
-          </cell>
-          <cell r="F10">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="C11">
-            <v>6.3999999999999986</v>
-          </cell>
-          <cell r="D11">
-            <v>0</v>
-          </cell>
-          <cell r="E11">
-            <v>-5</v>
-          </cell>
-          <cell r="F11">
-            <v>5</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -9500,7 +8308,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C56EA6D-9614-4348-98EA-ED615F0B8A5E}">
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:U46"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:21">
@@ -10863,6 +9671,646 @@
       </c>
       <c r="U21" s="3">
         <v>10.710145760568</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
+      <c r="B27">
+        <v>10.957459627946955</v>
+      </c>
+      <c r="C27">
+        <v>11.676993855702458</v>
+      </c>
+      <c r="D27">
+        <v>11.896558382262592</v>
+      </c>
+      <c r="E27">
+        <v>12.135051767303375</v>
+      </c>
+      <c r="F27">
+        <v>12.065209395417478</v>
+      </c>
+      <c r="G27">
+        <v>10.151869011509698</v>
+      </c>
+      <c r="H27">
+        <v>10.989688709572656</v>
+      </c>
+      <c r="I27">
+        <v>11.083849832915584</v>
+      </c>
+      <c r="J27">
+        <v>10.952939439279143</v>
+      </c>
+      <c r="K27">
+        <v>10.830298626218573</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
+      <c r="B28">
+        <v>11.720635958967032</v>
+      </c>
+      <c r="C28">
+        <v>13.244464773209765</v>
+      </c>
+      <c r="D28">
+        <v>11.796155851528747</v>
+      </c>
+      <c r="E28">
+        <v>9.1524571160459889</v>
+      </c>
+      <c r="F28">
+        <v>11.502459548695478</v>
+      </c>
+      <c r="G28">
+        <v>9.578714545399416</v>
+      </c>
+      <c r="H28">
+        <v>11.431039203502005</v>
+      </c>
+      <c r="I28">
+        <v>11.471600393464323</v>
+      </c>
+      <c r="J28">
+        <v>11.64840616348898</v>
+      </c>
+      <c r="K28">
+        <v>10.882707121539861</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
+      <c r="B29">
+        <v>11.056795776142971</v>
+      </c>
+      <c r="C29">
+        <v>11.168438524522353</v>
+      </c>
+      <c r="D29">
+        <v>11.255281626121141</v>
+      </c>
+      <c r="E29">
+        <v>11.607021880821558</v>
+      </c>
+      <c r="F29">
+        <v>12.786284079824108</v>
+      </c>
+      <c r="G29">
+        <v>12.724543031994253</v>
+      </c>
+      <c r="H29">
+        <v>11.376555923392297</v>
+      </c>
+      <c r="I29">
+        <v>11.540387751496164</v>
+      </c>
+      <c r="J29">
+        <v>10.445756308230338</v>
+      </c>
+      <c r="K29">
+        <v>10.770468654130818</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
+      <c r="B30">
+        <v>10.924255113253603</v>
+      </c>
+      <c r="C30">
+        <v>10.841793502380606</v>
+      </c>
+      <c r="D30">
+        <v>10.701756329411873</v>
+      </c>
+      <c r="E30">
+        <v>11.302000095214462</v>
+      </c>
+      <c r="F30">
+        <v>10.591466454401379</v>
+      </c>
+      <c r="G30">
+        <v>10.827109710420482</v>
+      </c>
+      <c r="H30">
+        <v>10.27882992440369</v>
+      </c>
+      <c r="I30">
+        <v>11.131895027405116</v>
+      </c>
+      <c r="J30">
+        <v>9.3587941790372131</v>
+      </c>
+      <c r="K30">
+        <v>11.757356807551114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
+      <c r="B31">
+        <v>11.547532969246967</v>
+      </c>
+      <c r="C31">
+        <v>11.740570945961517</v>
+      </c>
+      <c r="D31">
+        <v>8.7326798364426939</v>
+      </c>
+      <c r="E31">
+        <v>10.893266355027444</v>
+      </c>
+      <c r="F31">
+        <v>11.502632352688815</v>
+      </c>
+      <c r="G31">
+        <v>11.128504885904258</v>
+      </c>
+      <c r="H31">
+        <v>9.1424890541145576</v>
+      </c>
+      <c r="I31">
+        <v>11.393545284421416</v>
+      </c>
+      <c r="J31">
+        <v>10.619528913424583</v>
+      </c>
+      <c r="K31">
+        <v>11.852428562464192</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
+      <c r="B32">
+        <v>11.44243517211522</v>
+      </c>
+      <c r="C32">
+        <v>10.45604269330739</v>
+      </c>
+      <c r="D32">
+        <v>11.183951093529467</v>
+      </c>
+      <c r="E32">
+        <v>10.590631993012503</v>
+      </c>
+      <c r="F32">
+        <v>11.198103967957431</v>
+      </c>
+      <c r="G32">
+        <v>11.404354628951987</v>
+      </c>
+      <c r="H32">
+        <v>10.468839283761335</v>
+      </c>
+      <c r="I32">
+        <v>11.004377049006289</v>
+      </c>
+      <c r="J32">
+        <v>11.643162926533259</v>
+      </c>
+      <c r="K32">
+        <v>10.447998212670209</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11">
+      <c r="B33">
+        <v>12.219562014992116</v>
+      </c>
+      <c r="C33">
+        <v>11.473558080809889</v>
+      </c>
+      <c r="D33">
+        <v>7.8733346725255249</v>
+      </c>
+      <c r="E33">
+        <v>9.132329998295754</v>
+      </c>
+      <c r="F33">
+        <v>10.11250835455372</v>
+      </c>
+      <c r="G33">
+        <v>11.843299509395147</v>
+      </c>
+      <c r="H33">
+        <v>11.913803538676584</v>
+      </c>
+      <c r="I33">
+        <v>10.815039578859578</v>
+      </c>
+      <c r="J33">
+        <v>10.759668404547265</v>
+      </c>
+      <c r="K33">
+        <v>10.233186932795215</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11">
+      <c r="B34">
+        <v>11.230678657569806</v>
+      </c>
+      <c r="C34">
+        <v>10.42482201393228</v>
+      </c>
+      <c r="D34">
+        <v>11.075184622144443</v>
+      </c>
+      <c r="E34">
+        <v>10.053493517092429</v>
+      </c>
+      <c r="F34">
+        <v>11.097511580204591</v>
+      </c>
+      <c r="G34">
+        <v>11.566188979317085</v>
+      </c>
+      <c r="H34">
+        <v>10.720793190388358</v>
+      </c>
+      <c r="I34">
+        <v>10.120605131136253</v>
+      </c>
+      <c r="J34">
+        <v>10.996191596690332</v>
+      </c>
+      <c r="K34">
+        <v>10.693321902921307</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11">
+      <c r="B35">
+        <v>8.9684936227183787</v>
+      </c>
+      <c r="C35">
+        <v>11.310711917589069</v>
+      </c>
+      <c r="D35">
+        <v>11.097663920567138</v>
+      </c>
+      <c r="E35">
+        <v>10.296701495293528</v>
+      </c>
+      <c r="F35">
+        <v>11.072884737417334</v>
+      </c>
+      <c r="G35">
+        <v>11.561729044673266</v>
+      </c>
+      <c r="H35">
+        <v>11.912766714716563</v>
+      </c>
+      <c r="I35">
+        <v>11.312873104374157</v>
+      </c>
+      <c r="J35">
+        <v>9.0457461026869712</v>
+      </c>
+      <c r="K35">
+        <v>10.525212039113976</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11">
+      <c r="B36">
+        <v>11.244338131122058</v>
+      </c>
+      <c r="C36">
+        <v>11.931086211747024</v>
+      </c>
+      <c r="D36">
+        <v>12.484586497351993</v>
+      </c>
+      <c r="E36">
+        <v>11.68715745899477</v>
+      </c>
+      <c r="F36">
+        <v>11.708576059221523</v>
+      </c>
+      <c r="G36">
+        <v>9.7553361427469643</v>
+      </c>
+      <c r="H36">
+        <v>9.8837954481621271</v>
+      </c>
+      <c r="I36">
+        <v>12.025719135466497</v>
+      </c>
+      <c r="J36">
+        <v>12.057894784278469</v>
+      </c>
+      <c r="K36">
+        <v>10.477586349055636</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11">
+      <c r="B37">
+        <v>10.444410256071714</v>
+      </c>
+      <c r="C37">
+        <v>11.479615315523697</v>
+      </c>
+      <c r="D37">
+        <v>12.49533217725344</v>
+      </c>
+      <c r="E37">
+        <v>11.937300334296888</v>
+      </c>
+      <c r="F37">
+        <v>12.139094471252756</v>
+      </c>
+      <c r="G37">
+        <v>9.7148158800462259</v>
+      </c>
+      <c r="H37">
+        <v>10.140650394363329</v>
+      </c>
+      <c r="I37">
+        <v>10.827887328390498</v>
+      </c>
+      <c r="J37">
+        <v>9.8422997523937372</v>
+      </c>
+      <c r="K37">
+        <v>10.921644863459514</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11">
+      <c r="B38">
+        <v>11.808827386461198</v>
+      </c>
+      <c r="C38">
+        <v>10.706085524192313</v>
+      </c>
+      <c r="D38">
+        <v>11.148173845698475</v>
+      </c>
+      <c r="E38">
+        <v>11.712780198480468</v>
+      </c>
+      <c r="F38">
+        <v>11.562620349481003</v>
+      </c>
+      <c r="G38">
+        <v>10.854659441805561</v>
+      </c>
+      <c r="H38">
+        <v>10.177025634960737</v>
+      </c>
+      <c r="I38">
+        <v>10.964352460918017</v>
+      </c>
+      <c r="J38">
+        <v>10.032245447122259</v>
+      </c>
+      <c r="K38">
+        <v>10.620849954478908</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11">
+      <c r="B39">
+        <v>10.249325916278176</v>
+      </c>
+      <c r="C39">
+        <v>10.875686959310551</v>
+      </c>
+      <c r="D39">
+        <v>10.589462155452347</v>
+      </c>
+      <c r="E39">
+        <v>10.082110767883714</v>
+      </c>
+      <c r="F39">
+        <v>9.3790850058337671</v>
+      </c>
+      <c r="G39">
+        <v>12.813618943085894</v>
+      </c>
+      <c r="H39">
+        <v>12.758803697410039</v>
+      </c>
+      <c r="I39">
+        <v>10.288688846970908</v>
+      </c>
+      <c r="J39">
+        <v>11.622175199421472</v>
+      </c>
+      <c r="K39">
+        <v>10.915728600424481</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11">
+      <c r="B40">
+        <v>11.209172518478008</v>
+      </c>
+      <c r="C40">
+        <v>12.28509338199161</v>
+      </c>
+      <c r="D40">
+        <v>11.244417711908463</v>
+      </c>
+      <c r="E40">
+        <v>9.5012074069143271</v>
+      </c>
+      <c r="F40">
+        <v>12.54684140968835</v>
+      </c>
+      <c r="G40">
+        <v>9.6320473147113805</v>
+      </c>
+      <c r="H40">
+        <v>12.640623955861665</v>
+      </c>
+      <c r="I40">
+        <v>10.061919985504355</v>
+      </c>
+      <c r="J40">
+        <v>10.693000169170555</v>
+      </c>
+      <c r="K40">
+        <v>11.47313289203681</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11">
+      <c r="B41">
+        <v>12.424027792634442</v>
+      </c>
+      <c r="C41">
+        <v>11.138218289319193</v>
+      </c>
+      <c r="D41">
+        <v>11.396016836273484</v>
+      </c>
+      <c r="E41">
+        <v>11.521374764755601</v>
+      </c>
+      <c r="F41">
+        <v>9.7653565006237475</v>
+      </c>
+      <c r="G41">
+        <v>8.4858247844874857</v>
+      </c>
+      <c r="H41">
+        <v>9.6772764862305483</v>
+      </c>
+      <c r="I41">
+        <v>10.86448539518984</v>
+      </c>
+      <c r="J41">
+        <v>10.161557403820334</v>
+      </c>
+      <c r="K41">
+        <v>9.8034552336810155</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11">
+      <c r="B42">
+        <v>10.983107378536952</v>
+      </c>
+      <c r="C42">
+        <v>10.947498387225787</v>
+      </c>
+      <c r="D42">
+        <v>10.306828718797769</v>
+      </c>
+      <c r="E42">
+        <v>9.6885337569017427</v>
+      </c>
+      <c r="F42">
+        <v>11.335215978591586</v>
+      </c>
+      <c r="G42">
+        <v>11.342887566401041</v>
+      </c>
+      <c r="H42">
+        <v>11.446974687545444</v>
+      </c>
+      <c r="I42">
+        <v>10.534825398111716</v>
+      </c>
+      <c r="J42">
+        <v>12.102657839762978</v>
+      </c>
+      <c r="K42">
+        <v>12.32927208713023</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11">
+      <c r="B43">
+        <v>11.782579369368031</v>
+      </c>
+      <c r="C43">
+        <v>11.038422846298781</v>
+      </c>
+      <c r="D43">
+        <v>11.425445811086101</v>
+      </c>
+      <c r="E43">
+        <v>10.964276290736743</v>
+      </c>
+      <c r="F43">
+        <v>11.884945271789329</v>
+      </c>
+      <c r="G43">
+        <v>10.019833118179813</v>
+      </c>
+      <c r="H43">
+        <v>10.997339833751321</v>
+      </c>
+      <c r="I43">
+        <v>11.391158997697639</v>
+      </c>
+      <c r="J43">
+        <v>10.339274942283518</v>
+      </c>
+      <c r="K43">
+        <v>10.043045696705812</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11">
+      <c r="B44">
+        <v>8.5938727550581095</v>
+      </c>
+      <c r="C44">
+        <v>12.594940036991611</v>
+      </c>
+      <c r="D44">
+        <v>11.246619825955131</v>
+      </c>
+      <c r="E44">
+        <v>10.403075995612889</v>
+      </c>
+      <c r="F44">
+        <v>12.058160811478738</v>
+      </c>
+      <c r="G44">
+        <v>10.360582129409304</v>
+      </c>
+      <c r="H44">
+        <v>9.7961338013317434</v>
+      </c>
+      <c r="I44">
+        <v>10.481637011083658</v>
+      </c>
+      <c r="J44">
+        <v>9.7866523190657606</v>
+      </c>
+      <c r="K44">
+        <v>10.191975454121129</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11">
+      <c r="B45">
+        <v>12.237726897923276</v>
+      </c>
+      <c r="C45">
+        <v>11.595632733418606</v>
+      </c>
+      <c r="D45">
+        <v>11.52215920393588</v>
+      </c>
+      <c r="E45">
+        <v>11.105039922598516</v>
+      </c>
+      <c r="F45">
+        <v>11.562086021343712</v>
+      </c>
+      <c r="G45">
+        <v>11.282813167612185</v>
+      </c>
+      <c r="H45">
+        <v>11.402370793633745</v>
+      </c>
+      <c r="I45">
+        <v>12.119062850446207</v>
+      </c>
+      <c r="J45">
+        <v>13.078682078970596</v>
+      </c>
+      <c r="K45">
+        <v>10.920645556155941</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11">
+      <c r="B46">
+        <v>11.692941845298046</v>
+      </c>
+      <c r="C46">
+        <v>11.03260776454932</v>
+      </c>
+      <c r="D46">
+        <v>10.647122982676374</v>
+      </c>
+      <c r="E46">
+        <v>8.6665231918357311</v>
+      </c>
+      <c r="F46">
+        <v>10.472820596818346</v>
+      </c>
+      <c r="G46">
+        <v>11.552665929970098</v>
+      </c>
+      <c r="H46">
+        <v>10.183285232245689</v>
+      </c>
+      <c r="I46">
+        <v>10.7834380485781</v>
+      </c>
+      <c r="J46">
+        <v>11.064915290093049</v>
+      </c>
+      <c r="K46">
+        <v>8.6252321323752401</v>
       </c>
     </row>
   </sheetData>
@@ -11854,34 +11302,34 @@
       </c>
     </row>
     <row r="56" spans="1:24">
-      <c r="D56" s="13" t="s">
+      <c r="D56" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="14" t="s">
+      <c r="E56" s="17"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="H56" s="14"/>
-      <c r="I56" s="14"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
     </row>
     <row r="57" spans="1:24">
-      <c r="A57" s="15" t="s">
+      <c r="A57" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B57" s="15" t="s">
+      <c r="B57" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C57" s="15" t="s">
+      <c r="C57" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="16" t="s">
+      <c r="D57" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="E57" s="17" t="s">
+      <c r="E57" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="F57" s="17" t="s">
+      <c r="F57" s="13" t="s">
         <v>37</v>
       </c>
       <c r="G57" s="4" t="s">
@@ -11902,22 +11350,22 @@
         <v>305</v>
       </c>
       <c r="C58" s="8"/>
-      <c r="D58" s="18">
+      <c r="D58" s="16">
         <v>300.5</v>
       </c>
-      <c r="E58" s="18">
+      <c r="E58" s="16">
         <v>321.21668533034716</v>
       </c>
-      <c r="F58" s="18">
+      <c r="F58" s="16">
         <v>279.78331466965284</v>
       </c>
-      <c r="G58" s="18">
+      <c r="G58" s="16">
         <v>7.7894736842105265</v>
       </c>
-      <c r="H58" s="18">
+      <c r="H58" s="16">
         <v>25.448210526315791</v>
       </c>
-      <c r="I58" s="18">
+      <c r="I58" s="16">
         <v>0</v>
       </c>
       <c r="X58" t="s">
@@ -11935,22 +11383,22 @@
         <f>ABS(B59-B58)</f>
         <v>23</v>
       </c>
-      <c r="D59" s="18">
+      <c r="D59" s="16">
         <v>300.5</v>
       </c>
-      <c r="E59" s="18">
+      <c r="E59" s="16">
         <v>321.21668533034716</v>
       </c>
-      <c r="F59" s="18">
+      <c r="F59" s="16">
         <v>279.78331466965284</v>
       </c>
-      <c r="G59" s="18">
+      <c r="G59" s="16">
         <v>7.7894736842105265</v>
       </c>
-      <c r="H59" s="18">
+      <c r="H59" s="16">
         <v>25.448210526315791</v>
       </c>
-      <c r="I59" s="18">
+      <c r="I59" s="16">
         <v>0</v>
       </c>
     </row>
@@ -11965,22 +11413,22 @@
         <f t="shared" ref="C60:C77" si="2">ABS(B60-B59)</f>
         <v>23</v>
       </c>
-      <c r="D60" s="18">
+      <c r="D60" s="16">
         <v>300.5</v>
       </c>
-      <c r="E60" s="18">
+      <c r="E60" s="16">
         <v>321.21668533034716</v>
       </c>
-      <c r="F60" s="18">
+      <c r="F60" s="16">
         <v>279.78331466965284</v>
       </c>
-      <c r="G60" s="18">
+      <c r="G60" s="16">
         <v>7.7894736842105265</v>
       </c>
-      <c r="H60" s="18">
+      <c r="H60" s="16">
         <v>25.448210526315791</v>
       </c>
-      <c r="I60" s="18">
+      <c r="I60" s="16">
         <v>0</v>
       </c>
     </row>
@@ -11995,22 +11443,22 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="D61" s="18">
+      <c r="D61" s="16">
         <v>300.5</v>
       </c>
-      <c r="E61" s="18">
+      <c r="E61" s="16">
         <v>321.21668533034716</v>
       </c>
-      <c r="F61" s="18">
+      <c r="F61" s="16">
         <v>279.78331466965284</v>
       </c>
-      <c r="G61" s="18">
+      <c r="G61" s="16">
         <v>7.7894736842105265</v>
       </c>
-      <c r="H61" s="18">
+      <c r="H61" s="16">
         <v>25.448210526315791</v>
       </c>
-      <c r="I61" s="18">
+      <c r="I61" s="16">
         <v>0</v>
       </c>
     </row>
@@ -12025,22 +11473,22 @@
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="D62" s="18">
+      <c r="D62" s="16">
         <v>300.5</v>
       </c>
-      <c r="E62" s="18">
+      <c r="E62" s="16">
         <v>321.21668533034716</v>
       </c>
-      <c r="F62" s="18">
+      <c r="F62" s="16">
         <v>279.78331466965284</v>
       </c>
-      <c r="G62" s="18">
+      <c r="G62" s="16">
         <v>7.7894736842105265</v>
       </c>
-      <c r="H62" s="18">
+      <c r="H62" s="16">
         <v>25.448210526315791</v>
       </c>
-      <c r="I62" s="18">
+      <c r="I62" s="16">
         <v>0</v>
       </c>
     </row>
@@ -12055,22 +11503,22 @@
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="D63" s="18">
+      <c r="D63" s="16">
         <v>300.5</v>
       </c>
-      <c r="E63" s="18">
+      <c r="E63" s="16">
         <v>321.21668533034716</v>
       </c>
-      <c r="F63" s="18">
+      <c r="F63" s="16">
         <v>279.78331466965284</v>
       </c>
-      <c r="G63" s="18">
+      <c r="G63" s="16">
         <v>7.7894736842105265</v>
       </c>
-      <c r="H63" s="18">
+      <c r="H63" s="16">
         <v>25.448210526315791</v>
       </c>
-      <c r="I63" s="18">
+      <c r="I63" s="16">
         <v>0</v>
       </c>
     </row>
@@ -12085,22 +11533,22 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="D64" s="18">
+      <c r="D64" s="16">
         <v>300.5</v>
       </c>
-      <c r="E64" s="18">
+      <c r="E64" s="16">
         <v>321.21668533034716</v>
       </c>
-      <c r="F64" s="18">
+      <c r="F64" s="16">
         <v>279.78331466965284</v>
       </c>
-      <c r="G64" s="18">
+      <c r="G64" s="16">
         <v>7.7894736842105265</v>
       </c>
-      <c r="H64" s="18">
+      <c r="H64" s="16">
         <v>25.448210526315791</v>
       </c>
-      <c r="I64" s="18">
+      <c r="I64" s="16">
         <v>0</v>
       </c>
     </row>
@@ -12115,22 +11563,22 @@
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="D65" s="18">
+      <c r="D65" s="16">
         <v>300.5</v>
       </c>
-      <c r="E65" s="18">
+      <c r="E65" s="16">
         <v>321.21668533034716</v>
       </c>
-      <c r="F65" s="18">
+      <c r="F65" s="16">
         <v>279.78331466965284</v>
       </c>
-      <c r="G65" s="18">
+      <c r="G65" s="16">
         <v>7.7894736842105265</v>
       </c>
-      <c r="H65" s="18">
+      <c r="H65" s="16">
         <v>25.448210526315791</v>
       </c>
-      <c r="I65" s="18">
+      <c r="I65" s="16">
         <v>0</v>
       </c>
     </row>
@@ -12145,22 +11593,22 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="D66" s="18">
+      <c r="D66" s="16">
         <v>300.5</v>
       </c>
-      <c r="E66" s="18">
+      <c r="E66" s="16">
         <v>321.21668533034716</v>
       </c>
-      <c r="F66" s="18">
+      <c r="F66" s="16">
         <v>279.78331466965284</v>
       </c>
-      <c r="G66" s="18">
+      <c r="G66" s="16">
         <v>7.7894736842105265</v>
       </c>
-      <c r="H66" s="18">
+      <c r="H66" s="16">
         <v>25.448210526315791</v>
       </c>
-      <c r="I66" s="18">
+      <c r="I66" s="16">
         <v>0</v>
       </c>
     </row>
@@ -12175,22 +11623,22 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="D67" s="18">
+      <c r="D67" s="16">
         <v>300.5</v>
       </c>
-      <c r="E67" s="18">
+      <c r="E67" s="16">
         <v>321.21668533034716</v>
       </c>
-      <c r="F67" s="18">
+      <c r="F67" s="16">
         <v>279.78331466965284</v>
       </c>
-      <c r="G67" s="18">
+      <c r="G67" s="16">
         <v>7.7894736842105265</v>
       </c>
-      <c r="H67" s="18">
+      <c r="H67" s="16">
         <v>25.448210526315791</v>
       </c>
-      <c r="I67" s="18">
+      <c r="I67" s="16">
         <v>0</v>
       </c>
     </row>
@@ -12205,22 +11653,22 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="D68" s="18">
+      <c r="D68" s="16">
         <v>300.5</v>
       </c>
-      <c r="E68" s="18">
+      <c r="E68" s="16">
         <v>321.21668533034716</v>
       </c>
-      <c r="F68" s="18">
+      <c r="F68" s="16">
         <v>279.78331466965284</v>
       </c>
-      <c r="G68" s="18">
+      <c r="G68" s="16">
         <v>7.7894736842105265</v>
       </c>
-      <c r="H68" s="18">
+      <c r="H68" s="16">
         <v>25.448210526315791</v>
       </c>
-      <c r="I68" s="18">
+      <c r="I68" s="16">
         <v>0</v>
       </c>
     </row>
@@ -12235,22 +11683,22 @@
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="D69" s="18">
+      <c r="D69" s="16">
         <v>300.5</v>
       </c>
-      <c r="E69" s="18">
+      <c r="E69" s="16">
         <v>321.21668533034716</v>
       </c>
-      <c r="F69" s="18">
+      <c r="F69" s="16">
         <v>279.78331466965284</v>
       </c>
-      <c r="G69" s="18">
+      <c r="G69" s="16">
         <v>7.7894736842105265</v>
       </c>
-      <c r="H69" s="18">
+      <c r="H69" s="16">
         <v>25.448210526315791</v>
       </c>
-      <c r="I69" s="18">
+      <c r="I69" s="16">
         <v>0</v>
       </c>
     </row>
@@ -12265,22 +11713,22 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="D70" s="18">
+      <c r="D70" s="16">
         <v>300.5</v>
       </c>
-      <c r="E70" s="18">
+      <c r="E70" s="16">
         <v>321.21668533034716</v>
       </c>
-      <c r="F70" s="18">
+      <c r="F70" s="16">
         <v>279.78331466965284</v>
       </c>
-      <c r="G70" s="18">
+      <c r="G70" s="16">
         <v>7.7894736842105265</v>
       </c>
-      <c r="H70" s="18">
+      <c r="H70" s="16">
         <v>25.448210526315791</v>
       </c>
-      <c r="I70" s="18">
+      <c r="I70" s="16">
         <v>0</v>
       </c>
     </row>
@@ -12295,22 +11743,22 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="D71" s="18">
+      <c r="D71" s="16">
         <v>300.5</v>
       </c>
-      <c r="E71" s="18">
+      <c r="E71" s="16">
         <v>321.21668533034716</v>
       </c>
-      <c r="F71" s="18">
+      <c r="F71" s="16">
         <v>279.78331466965284</v>
       </c>
-      <c r="G71" s="18">
+      <c r="G71" s="16">
         <v>7.7894736842105265</v>
       </c>
-      <c r="H71" s="18">
+      <c r="H71" s="16">
         <v>25.448210526315791</v>
       </c>
-      <c r="I71" s="18">
+      <c r="I71" s="16">
         <v>0</v>
       </c>
     </row>
@@ -12325,22 +11773,22 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="D72" s="18">
+      <c r="D72" s="16">
         <v>300.5</v>
       </c>
-      <c r="E72" s="18">
+      <c r="E72" s="16">
         <v>321.21668533034716</v>
       </c>
-      <c r="F72" s="18">
+      <c r="F72" s="16">
         <v>279.78331466965284</v>
       </c>
-      <c r="G72" s="18">
+      <c r="G72" s="16">
         <v>7.7894736842105265</v>
       </c>
-      <c r="H72" s="18">
+      <c r="H72" s="16">
         <v>25.448210526315791</v>
       </c>
-      <c r="I72" s="18">
+      <c r="I72" s="16">
         <v>0</v>
       </c>
     </row>
@@ -12355,22 +11803,22 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="D73" s="18">
+      <c r="D73" s="16">
         <v>300.5</v>
       </c>
-      <c r="E73" s="18">
+      <c r="E73" s="16">
         <v>321.21668533034716</v>
       </c>
-      <c r="F73" s="18">
+      <c r="F73" s="16">
         <v>279.78331466965284</v>
       </c>
-      <c r="G73" s="18">
+      <c r="G73" s="16">
         <v>7.7894736842105265</v>
       </c>
-      <c r="H73" s="18">
+      <c r="H73" s="16">
         <v>25.448210526315791</v>
       </c>
-      <c r="I73" s="18">
+      <c r="I73" s="16">
         <v>0</v>
       </c>
       <c r="X73" t="s">
@@ -12388,22 +11836,22 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="D74" s="18">
+      <c r="D74" s="16">
         <v>300.5</v>
       </c>
-      <c r="E74" s="18">
+      <c r="E74" s="16">
         <v>321.21668533034716</v>
       </c>
-      <c r="F74" s="18">
+      <c r="F74" s="16">
         <v>279.78331466965284</v>
       </c>
-      <c r="G74" s="18">
+      <c r="G74" s="16">
         <v>7.7894736842105265</v>
       </c>
-      <c r="H74" s="18">
+      <c r="H74" s="16">
         <v>25.448210526315791</v>
       </c>
-      <c r="I74" s="18">
+      <c r="I74" s="16">
         <v>0</v>
       </c>
     </row>
@@ -12418,22 +11866,22 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="D75" s="18">
+      <c r="D75" s="16">
         <v>300.5</v>
       </c>
-      <c r="E75" s="18">
+      <c r="E75" s="16">
         <v>321.21668533034716</v>
       </c>
-      <c r="F75" s="18">
+      <c r="F75" s="16">
         <v>279.78331466965284</v>
       </c>
-      <c r="G75" s="18">
+      <c r="G75" s="16">
         <v>7.7894736842105265</v>
       </c>
-      <c r="H75" s="18">
+      <c r="H75" s="16">
         <v>25.448210526315791</v>
       </c>
-      <c r="I75" s="18">
+      <c r="I75" s="16">
         <v>0</v>
       </c>
     </row>
@@ -12448,22 +11896,22 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="D76" s="18">
+      <c r="D76" s="16">
         <v>300.5</v>
       </c>
-      <c r="E76" s="18">
+      <c r="E76" s="16">
         <v>321.21668533034716</v>
       </c>
-      <c r="F76" s="18">
+      <c r="F76" s="16">
         <v>279.78331466965284</v>
       </c>
-      <c r="G76" s="18">
+      <c r="G76" s="16">
         <v>7.7894736842105265</v>
       </c>
-      <c r="H76" s="18">
+      <c r="H76" s="16">
         <v>25.448210526315791</v>
       </c>
-      <c r="I76" s="18">
+      <c r="I76" s="16">
         <v>0</v>
       </c>
     </row>
@@ -12478,22 +11926,22 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="D77" s="18">
+      <c r="D77" s="16">
         <v>300.5</v>
       </c>
-      <c r="E77" s="18">
+      <c r="E77" s="16">
         <v>321.21668533034716</v>
       </c>
-      <c r="F77" s="18">
+      <c r="F77" s="16">
         <v>279.78331466965284</v>
       </c>
-      <c r="G77" s="18">
+      <c r="G77" s="16">
         <v>7.7894736842105265</v>
       </c>
-      <c r="H77" s="18">
+      <c r="H77" s="16">
         <v>25.448210526315791</v>
       </c>
-      <c r="I77" s="18">
+      <c r="I77" s="16">
         <v>0</v>
       </c>
     </row>
@@ -12505,4 +11953,2779 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84BAA8E1-EBB0-4D6B-905D-0D0B8FE524CC}">
+  <dimension ref="A1:C103"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="3" width="19.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="42" thickBot="1">
+      <c r="A1" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" thickBot="1">
+      <c r="A2" s="21">
+        <v>1</v>
+      </c>
+      <c r="B2" s="21">
+        <v>12</v>
+      </c>
+      <c r="C2" s="22">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickBot="1">
+      <c r="A3" s="21">
+        <v>2</v>
+      </c>
+      <c r="B3" s="21">
+        <v>15</v>
+      </c>
+      <c r="C3" s="22">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1">
+      <c r="A4" s="21">
+        <v>3</v>
+      </c>
+      <c r="B4" s="21">
+        <v>8</v>
+      </c>
+      <c r="C4" s="22">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" thickBot="1">
+      <c r="A5" s="21">
+        <v>4</v>
+      </c>
+      <c r="B5" s="21">
+        <v>10</v>
+      </c>
+      <c r="C5" s="22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" thickBot="1">
+      <c r="A6" s="21">
+        <v>5</v>
+      </c>
+      <c r="B6" s="21">
+        <v>4</v>
+      </c>
+      <c r="C6" s="22">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1">
+      <c r="A7" s="21">
+        <v>6</v>
+      </c>
+      <c r="B7" s="21">
+        <v>7</v>
+      </c>
+      <c r="C7" s="22">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" thickBot="1">
+      <c r="A8" s="21">
+        <v>7</v>
+      </c>
+      <c r="B8" s="21">
+        <v>16</v>
+      </c>
+      <c r="C8" s="22">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" thickBot="1">
+      <c r="A9" s="21">
+        <v>8</v>
+      </c>
+      <c r="B9" s="21">
+        <v>9</v>
+      </c>
+      <c r="C9" s="22">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="21">
+        <v>9</v>
+      </c>
+      <c r="B10" s="21">
+        <v>14</v>
+      </c>
+      <c r="C10" s="22">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="21">
+        <v>10</v>
+      </c>
+      <c r="B11" s="21">
+        <v>10</v>
+      </c>
+      <c r="C11" s="22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" thickBot="1">
+      <c r="A12" s="21">
+        <v>11</v>
+      </c>
+      <c r="B12" s="21">
+        <v>5</v>
+      </c>
+      <c r="C12" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="21">
+        <v>12</v>
+      </c>
+      <c r="B13" s="21">
+        <v>6</v>
+      </c>
+      <c r="C13" s="22">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15" thickBot="1">
+      <c r="A14" s="21">
+        <v>13</v>
+      </c>
+      <c r="B14" s="21">
+        <v>17</v>
+      </c>
+      <c r="C14" s="22">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="21">
+        <v>14</v>
+      </c>
+      <c r="B15" s="21">
+        <v>12</v>
+      </c>
+      <c r="C15" s="22">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15" thickBot="1">
+      <c r="A16" s="21">
+        <v>15</v>
+      </c>
+      <c r="B16" s="21">
+        <v>22</v>
+      </c>
+      <c r="C16" s="22">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="21">
+        <v>16</v>
+      </c>
+      <c r="B17" s="21">
+        <v>8</v>
+      </c>
+      <c r="C17" s="22">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15" thickBot="1">
+      <c r="A18" s="21">
+        <v>17</v>
+      </c>
+      <c r="B18" s="21">
+        <v>10</v>
+      </c>
+      <c r="C18" s="22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="21">
+        <v>18</v>
+      </c>
+      <c r="B19" s="21">
+        <v>5</v>
+      </c>
+      <c r="C19" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15" thickBot="1">
+      <c r="A20" s="21">
+        <v>19</v>
+      </c>
+      <c r="B20" s="21">
+        <v>13</v>
+      </c>
+      <c r="C20" s="22">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15" thickBot="1">
+      <c r="A21" s="21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="21">
+        <v>11</v>
+      </c>
+      <c r="C21" s="22">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15" thickBot="1">
+      <c r="A22" s="21">
+        <v>21</v>
+      </c>
+      <c r="B22" s="21">
+        <v>20</v>
+      </c>
+      <c r="C22" s="22">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15" thickBot="1">
+      <c r="A23" s="21">
+        <v>22</v>
+      </c>
+      <c r="B23" s="21">
+        <v>18</v>
+      </c>
+      <c r="C23" s="22">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15" thickBot="1">
+      <c r="A24" s="21">
+        <v>23</v>
+      </c>
+      <c r="B24" s="21">
+        <v>24</v>
+      </c>
+      <c r="C24" s="22">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15" thickBot="1">
+      <c r="A25" s="21">
+        <v>24</v>
+      </c>
+      <c r="B25" s="21">
+        <v>15</v>
+      </c>
+      <c r="C25" s="22">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15" thickBot="1">
+      <c r="A26" s="21">
+        <v>25</v>
+      </c>
+      <c r="B26" s="21">
+        <v>9</v>
+      </c>
+      <c r="C26" s="22">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15" thickBot="1">
+      <c r="A27" s="21">
+        <v>26</v>
+      </c>
+      <c r="B27" s="21">
+        <v>12</v>
+      </c>
+      <c r="C27" s="22">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15" thickBot="1">
+      <c r="A28" s="21">
+        <v>27</v>
+      </c>
+      <c r="B28" s="21">
+        <v>7</v>
+      </c>
+      <c r="C28" s="22">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15" thickBot="1">
+      <c r="A29" s="21">
+        <v>28</v>
+      </c>
+      <c r="B29" s="21">
+        <v>13</v>
+      </c>
+      <c r="C29" s="22">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15" thickBot="1">
+      <c r="A30" s="21">
+        <v>29</v>
+      </c>
+      <c r="B30" s="21">
+        <v>9</v>
+      </c>
+      <c r="C30" s="22">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15" thickBot="1">
+      <c r="A31" s="21">
+        <v>30</v>
+      </c>
+      <c r="B31" s="21">
+        <v>6</v>
+      </c>
+      <c r="C31" s="22">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="42" thickBot="1">
+      <c r="A32" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="19">
+        <f>SUM(B2:B31)</f>
+        <v>347</v>
+      </c>
+      <c r="C32" s="20">
+        <f>AVERAGE(C2:C31)</f>
+        <v>0.23133333333333334</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15" thickBot="1"/>
+    <row r="35" spans="1:3" ht="42" thickBot="1">
+      <c r="A35" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15" thickBot="1">
+      <c r="A36" s="21">
+        <v>31</v>
+      </c>
+      <c r="B36" s="21">
+        <v>9</v>
+      </c>
+      <c r="C36" s="22">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="15" thickBot="1">
+      <c r="A37" s="21">
+        <v>32</v>
+      </c>
+      <c r="B37" s="21">
+        <v>6</v>
+      </c>
+      <c r="C37" s="22">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="15" thickBot="1">
+      <c r="A38" s="21">
+        <v>33</v>
+      </c>
+      <c r="B38" s="21">
+        <v>12</v>
+      </c>
+      <c r="C38" s="22">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="15" thickBot="1">
+      <c r="A39" s="21">
+        <v>34</v>
+      </c>
+      <c r="B39" s="21">
+        <v>5</v>
+      </c>
+      <c r="C39" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="15" thickBot="1">
+      <c r="A40" s="21">
+        <v>35</v>
+      </c>
+      <c r="B40" s="21">
+        <v>6</v>
+      </c>
+      <c r="C40" s="22">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="15" thickBot="1">
+      <c r="A41" s="21">
+        <v>36</v>
+      </c>
+      <c r="B41" s="21">
+        <v>4</v>
+      </c>
+      <c r="C41" s="22">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15" thickBot="1">
+      <c r="A42" s="21">
+        <v>37</v>
+      </c>
+      <c r="B42" s="21">
+        <v>6</v>
+      </c>
+      <c r="C42" s="22">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="15" thickBot="1">
+      <c r="A43" s="21">
+        <v>38</v>
+      </c>
+      <c r="B43" s="21">
+        <v>3</v>
+      </c>
+      <c r="C43" s="22">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="15" thickBot="1">
+      <c r="A44" s="21">
+        <v>39</v>
+      </c>
+      <c r="B44" s="21">
+        <v>7</v>
+      </c>
+      <c r="C44" s="22">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="15" thickBot="1">
+      <c r="A45" s="21">
+        <v>40</v>
+      </c>
+      <c r="B45" s="21">
+        <v>6</v>
+      </c>
+      <c r="C45" s="22">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="15" thickBot="1">
+      <c r="A46" s="21">
+        <v>41</v>
+      </c>
+      <c r="B46" s="21">
+        <v>2</v>
+      </c>
+      <c r="C46" s="22">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="15" thickBot="1">
+      <c r="A47" s="21">
+        <v>42</v>
+      </c>
+      <c r="B47" s="21">
+        <v>4</v>
+      </c>
+      <c r="C47" s="22">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="15" thickBot="1">
+      <c r="A48" s="21">
+        <v>43</v>
+      </c>
+      <c r="B48" s="21">
+        <v>3</v>
+      </c>
+      <c r="C48" s="22">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="15" thickBot="1">
+      <c r="A49" s="21">
+        <v>44</v>
+      </c>
+      <c r="B49" s="21">
+        <v>6</v>
+      </c>
+      <c r="C49" s="22">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="15" thickBot="1">
+      <c r="A50" s="21">
+        <v>45</v>
+      </c>
+      <c r="B50" s="21">
+        <v>5</v>
+      </c>
+      <c r="C50" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="15" thickBot="1">
+      <c r="A51" s="21">
+        <v>46</v>
+      </c>
+      <c r="B51" s="21">
+        <v>4</v>
+      </c>
+      <c r="C51" s="22">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="15" thickBot="1">
+      <c r="A52" s="21">
+        <v>47</v>
+      </c>
+      <c r="B52" s="21">
+        <v>8</v>
+      </c>
+      <c r="C52" s="22">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="15" thickBot="1">
+      <c r="A53" s="21">
+        <v>48</v>
+      </c>
+      <c r="B53" s="21">
+        <v>5</v>
+      </c>
+      <c r="C53" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="15" thickBot="1">
+      <c r="A54" s="21">
+        <v>49</v>
+      </c>
+      <c r="B54" s="21">
+        <v>6</v>
+      </c>
+      <c r="C54" s="22">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="15" thickBot="1">
+      <c r="A55" s="21">
+        <v>50</v>
+      </c>
+      <c r="B55" s="21">
+        <v>7</v>
+      </c>
+      <c r="C55" s="22">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="15" thickBot="1">
+      <c r="A56" s="21">
+        <v>51</v>
+      </c>
+      <c r="B56" s="21">
+        <v>5</v>
+      </c>
+      <c r="C56" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="15" thickBot="1">
+      <c r="A57" s="21">
+        <v>52</v>
+      </c>
+      <c r="B57" s="21">
+        <v>6</v>
+      </c>
+      <c r="C57" s="22">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="15" thickBot="1">
+      <c r="A58" s="21">
+        <v>53</v>
+      </c>
+      <c r="B58" s="21">
+        <v>3</v>
+      </c>
+      <c r="C58" s="22">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="15" thickBot="1">
+      <c r="A59" s="21">
+        <v>54</v>
+      </c>
+      <c r="B59" s="21">
+        <v>5</v>
+      </c>
+      <c r="C59" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="15" thickBot="1">
+      <c r="A60" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B60" s="19">
+        <f>SUM(B36:B59)</f>
+        <v>133</v>
+      </c>
+      <c r="C60" s="20">
+        <f>AVERAGE(C36:C59)</f>
+        <v>0.11083333333333338</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="15" thickBot="1"/>
+    <row r="63" spans="1:3" ht="42" thickBot="1">
+      <c r="A63" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B63" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C63" s="20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="15" thickBot="1">
+      <c r="A64" s="21">
+        <v>55</v>
+      </c>
+      <c r="B64" s="21">
+        <v>8</v>
+      </c>
+      <c r="C64" s="22">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="15" thickBot="1">
+      <c r="A65" s="21">
+        <v>56</v>
+      </c>
+      <c r="B65" s="21">
+        <v>7</v>
+      </c>
+      <c r="C65" s="22">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="15" thickBot="1">
+      <c r="A66" s="21">
+        <v>57</v>
+      </c>
+      <c r="B66" s="21">
+        <v>5</v>
+      </c>
+      <c r="C66" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="15" thickBot="1">
+      <c r="A67" s="21">
+        <v>58</v>
+      </c>
+      <c r="B67" s="21">
+        <v>6</v>
+      </c>
+      <c r="C67" s="22">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="15" thickBot="1">
+      <c r="A68" s="21">
+        <v>59</v>
+      </c>
+      <c r="B68" s="21">
+        <v>4</v>
+      </c>
+      <c r="C68" s="22">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="15" thickBot="1">
+      <c r="A69" s="21">
+        <v>60</v>
+      </c>
+      <c r="B69" s="21">
+        <v>5</v>
+      </c>
+      <c r="C69" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="15" thickBot="1">
+      <c r="A70" s="21">
+        <v>61</v>
+      </c>
+      <c r="B70" s="21">
+        <v>2</v>
+      </c>
+      <c r="C70" s="22">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="15" thickBot="1">
+      <c r="A71" s="21">
+        <v>62</v>
+      </c>
+      <c r="B71" s="21">
+        <v>3</v>
+      </c>
+      <c r="C71" s="22">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="15" thickBot="1">
+      <c r="A72" s="21">
+        <v>63</v>
+      </c>
+      <c r="B72" s="21">
+        <v>4</v>
+      </c>
+      <c r="C72" s="22">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="15" thickBot="1">
+      <c r="A73" s="21">
+        <v>64</v>
+      </c>
+      <c r="B73" s="21">
+        <v>7</v>
+      </c>
+      <c r="C73" s="22">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="15" thickBot="1">
+      <c r="A74" s="21">
+        <v>65</v>
+      </c>
+      <c r="B74" s="21">
+        <v>6</v>
+      </c>
+      <c r="C74" s="22">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="15" thickBot="1">
+      <c r="A75" s="21">
+        <v>66</v>
+      </c>
+      <c r="B75" s="21">
+        <v>5</v>
+      </c>
+      <c r="C75" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="15" thickBot="1">
+      <c r="A76" s="21">
+        <v>67</v>
+      </c>
+      <c r="B76" s="21">
+        <v>5</v>
+      </c>
+      <c r="C76" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="15" thickBot="1">
+      <c r="A77" s="21">
+        <v>68</v>
+      </c>
+      <c r="B77" s="21">
+        <v>3</v>
+      </c>
+      <c r="C77" s="22">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="15" thickBot="1">
+      <c r="A78" s="21">
+        <v>69</v>
+      </c>
+      <c r="B78" s="21">
+        <v>7</v>
+      </c>
+      <c r="C78" s="22">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="15" thickBot="1">
+      <c r="A79" s="21">
+        <v>70</v>
+      </c>
+      <c r="B79" s="21">
+        <v>9</v>
+      </c>
+      <c r="C79" s="22">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="15" thickBot="1">
+      <c r="A80" s="21">
+        <v>71</v>
+      </c>
+      <c r="B80" s="21">
+        <v>6</v>
+      </c>
+      <c r="C80" s="22">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="15" thickBot="1">
+      <c r="A81" s="21">
+        <v>72</v>
+      </c>
+      <c r="B81" s="21">
+        <v>10</v>
+      </c>
+      <c r="C81" s="22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="15" thickBot="1">
+      <c r="A82" s="21">
+        <v>73</v>
+      </c>
+      <c r="B82" s="21">
+        <v>4</v>
+      </c>
+      <c r="C82" s="22">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="15" thickBot="1">
+      <c r="A83" s="21">
+        <v>74</v>
+      </c>
+      <c r="B83" s="21">
+        <v>3</v>
+      </c>
+      <c r="C83" s="22">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="15" thickBot="1">
+      <c r="A84" s="21">
+        <v>75</v>
+      </c>
+      <c r="B84" s="21">
+        <v>5</v>
+      </c>
+      <c r="C84" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="15" thickBot="1">
+      <c r="A85" s="21">
+        <v>76</v>
+      </c>
+      <c r="B85" s="21">
+        <v>8</v>
+      </c>
+      <c r="C85" s="22">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="15" thickBot="1">
+      <c r="A86" s="21">
+        <v>77</v>
+      </c>
+      <c r="B86" s="21">
+        <v>11</v>
+      </c>
+      <c r="C86" s="22">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="15" thickBot="1">
+      <c r="A87" s="21">
+        <v>78</v>
+      </c>
+      <c r="B87" s="21">
+        <v>9</v>
+      </c>
+      <c r="C87" s="22">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="15" thickBot="1">
+      <c r="A88" s="21">
+        <v>79</v>
+      </c>
+      <c r="B88" s="21">
+        <v>7</v>
+      </c>
+      <c r="C88" s="22">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="15" thickBot="1">
+      <c r="A89" s="21">
+        <v>80</v>
+      </c>
+      <c r="B89" s="21">
+        <v>3</v>
+      </c>
+      <c r="C89" s="22">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="15" thickBot="1">
+      <c r="A90" s="21">
+        <v>81</v>
+      </c>
+      <c r="B90" s="21">
+        <v>5</v>
+      </c>
+      <c r="C90" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="15" thickBot="1">
+      <c r="A91" s="21">
+        <v>82</v>
+      </c>
+      <c r="B91" s="21">
+        <v>2</v>
+      </c>
+      <c r="C91" s="22">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="15" thickBot="1">
+      <c r="A92" s="21">
+        <v>83</v>
+      </c>
+      <c r="B92" s="21">
+        <v>1</v>
+      </c>
+      <c r="C92" s="22">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="15" thickBot="1">
+      <c r="A93" s="21">
+        <v>84</v>
+      </c>
+      <c r="B93" s="21">
+        <v>4</v>
+      </c>
+      <c r="C93" s="22">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="15" thickBot="1">
+      <c r="A94" s="21">
+        <v>85</v>
+      </c>
+      <c r="B94" s="21">
+        <v>5</v>
+      </c>
+      <c r="C94" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="15" thickBot="1">
+      <c r="A95" s="21">
+        <v>86</v>
+      </c>
+      <c r="B95" s="21">
+        <v>3</v>
+      </c>
+      <c r="C95" s="22">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="15" thickBot="1">
+      <c r="A96" s="21">
+        <v>87</v>
+      </c>
+      <c r="B96" s="21">
+        <v>7</v>
+      </c>
+      <c r="C96" s="22">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="15" thickBot="1">
+      <c r="A97" s="21">
+        <v>88</v>
+      </c>
+      <c r="B97" s="21">
+        <v>6</v>
+      </c>
+      <c r="C97" s="22">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="15" thickBot="1">
+      <c r="A98" s="21">
+        <v>89</v>
+      </c>
+      <c r="B98" s="21">
+        <v>4</v>
+      </c>
+      <c r="C98" s="22">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="15" thickBot="1">
+      <c r="A99" s="21">
+        <v>90</v>
+      </c>
+      <c r="B99" s="21">
+        <v>4</v>
+      </c>
+      <c r="C99" s="22">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="15" thickBot="1">
+      <c r="A100" s="21">
+        <v>91</v>
+      </c>
+      <c r="B100" s="21">
+        <v>6</v>
+      </c>
+      <c r="C100" s="22">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="15" thickBot="1">
+      <c r="A101" s="21">
+        <v>92</v>
+      </c>
+      <c r="B101" s="21">
+        <v>8</v>
+      </c>
+      <c r="C101" s="22">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="15" thickBot="1">
+      <c r="A102" s="21">
+        <v>93</v>
+      </c>
+      <c r="B102" s="21">
+        <v>5</v>
+      </c>
+      <c r="C102" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="15" thickBot="1">
+      <c r="A103" s="21">
+        <v>94</v>
+      </c>
+      <c r="B103" s="21">
+        <v>6</v>
+      </c>
+      <c r="C103" s="22">
+        <v>0.12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75572297-60F2-4440-A161-D86C48A55BF0}">
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="4" width="12.88671875" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A1" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" thickBot="1">
+      <c r="A2" s="21">
+        <v>1</v>
+      </c>
+      <c r="B2" s="21">
+        <v>100</v>
+      </c>
+      <c r="C2" s="21">
+        <v>12</v>
+      </c>
+      <c r="D2" s="23">
+        <f>C2/B2</f>
+        <v>0.12</v>
+      </c>
+      <c r="E2" s="25">
+        <f>SQRT(($D$30*(1-$D$30)/B2))</f>
+        <v>2.9352024271484114E-2</v>
+      </c>
+      <c r="F2" s="25">
+        <f>$D$30+(3*E2)</f>
+        <v>0.18327728493566448</v>
+      </c>
+      <c r="G2" s="25">
+        <f>$D$30-(3*E2)</f>
+        <v>7.165139306759799E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" thickBot="1">
+      <c r="A3" s="21">
+        <v>2</v>
+      </c>
+      <c r="B3" s="21">
+        <v>80</v>
+      </c>
+      <c r="C3" s="21">
+        <v>8</v>
+      </c>
+      <c r="D3" s="23">
+        <f t="shared" ref="D3:D26" si="0">C3/B3</f>
+        <v>0.1</v>
+      </c>
+      <c r="E3" s="25">
+        <f t="shared" ref="E3:E26" si="1">SQRT(($D$30*(1-$D$30)/B3))</f>
+        <v>3.2816560774131108E-2</v>
+      </c>
+      <c r="F3" s="25">
+        <f t="shared" ref="F3:F26" si="2">$D$30+(3*E3)</f>
+        <v>0.19367089444360547</v>
+      </c>
+      <c r="G3" s="25">
+        <f t="shared" ref="G3:G26" si="3">$D$30-(3*E3)</f>
+        <v>-3.22847020118118E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" thickBot="1">
+      <c r="A4" s="21">
+        <v>3</v>
+      </c>
+      <c r="B4" s="21">
+        <v>80</v>
+      </c>
+      <c r="C4" s="21">
+        <v>6</v>
+      </c>
+      <c r="D4" s="23">
+        <f t="shared" si="0"/>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="E4" s="25">
+        <f t="shared" si="1"/>
+        <v>3.2816560774131108E-2</v>
+      </c>
+      <c r="F4" s="25">
+        <f t="shared" si="2"/>
+        <v>0.19367089444360547</v>
+      </c>
+      <c r="G4" s="25">
+        <f t="shared" si="3"/>
+        <v>-3.22847020118118E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" thickBot="1">
+      <c r="A5" s="21">
+        <v>4</v>
+      </c>
+      <c r="B5" s="21">
+        <v>100</v>
+      </c>
+      <c r="C5" s="21">
+        <v>9</v>
+      </c>
+      <c r="D5" s="23">
+        <f t="shared" si="0"/>
+        <v>0.09</v>
+      </c>
+      <c r="E5" s="25">
+        <f t="shared" si="1"/>
+        <v>2.9352024271484114E-2</v>
+      </c>
+      <c r="F5" s="25">
+        <f t="shared" si="2"/>
+        <v>0.18327728493566448</v>
+      </c>
+      <c r="G5" s="25">
+        <f t="shared" si="3"/>
+        <v>7.165139306759799E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickBot="1">
+      <c r="A6" s="21">
+        <v>5</v>
+      </c>
+      <c r="B6" s="21">
+        <v>110</v>
+      </c>
+      <c r="C6" s="21">
+        <v>10</v>
+      </c>
+      <c r="D6" s="23">
+        <f t="shared" si="0"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="E6" s="25">
+        <f t="shared" si="1"/>
+        <v>2.7986057061488715E-2</v>
+      </c>
+      <c r="F6" s="25">
+        <f t="shared" si="2"/>
+        <v>0.17917938330567829</v>
+      </c>
+      <c r="G6" s="25">
+        <f t="shared" si="3"/>
+        <v>1.1263040936745988E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" thickBot="1">
+      <c r="A7" s="21">
+        <v>6</v>
+      </c>
+      <c r="B7" s="21">
+        <v>110</v>
+      </c>
+      <c r="C7" s="21">
+        <v>12</v>
+      </c>
+      <c r="D7" s="23">
+        <f t="shared" si="0"/>
+        <v>0.10909090909090909</v>
+      </c>
+      <c r="E7" s="25">
+        <f t="shared" si="1"/>
+        <v>2.7986057061488715E-2</v>
+      </c>
+      <c r="F7" s="25">
+        <f t="shared" si="2"/>
+        <v>0.17917938330567829</v>
+      </c>
+      <c r="G7" s="25">
+        <f t="shared" si="3"/>
+        <v>1.1263040936745988E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" thickBot="1">
+      <c r="A8" s="21">
+        <v>7</v>
+      </c>
+      <c r="B8" s="21">
+        <v>100</v>
+      </c>
+      <c r="C8" s="21">
+        <v>11</v>
+      </c>
+      <c r="D8" s="23">
+        <f t="shared" si="0"/>
+        <v>0.11</v>
+      </c>
+      <c r="E8" s="25">
+        <f t="shared" si="1"/>
+        <v>2.9352024271484114E-2</v>
+      </c>
+      <c r="F8" s="25">
+        <f t="shared" si="2"/>
+        <v>0.18327728493566448</v>
+      </c>
+      <c r="G8" s="25">
+        <f t="shared" si="3"/>
+        <v>7.165139306759799E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" thickBot="1">
+      <c r="A9" s="21">
+        <v>8</v>
+      </c>
+      <c r="B9" s="21">
+        <v>100</v>
+      </c>
+      <c r="C9" s="21">
+        <v>16</v>
+      </c>
+      <c r="D9" s="23">
+        <f t="shared" si="0"/>
+        <v>0.16</v>
+      </c>
+      <c r="E9" s="25">
+        <f t="shared" si="1"/>
+        <v>2.9352024271484114E-2</v>
+      </c>
+      <c r="F9" s="25">
+        <f t="shared" si="2"/>
+        <v>0.18327728493566448</v>
+      </c>
+      <c r="G9" s="25">
+        <f t="shared" si="3"/>
+        <v>7.165139306759799E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" thickBot="1">
+      <c r="A10" s="21">
+        <v>9</v>
+      </c>
+      <c r="B10" s="21">
+        <v>90</v>
+      </c>
+      <c r="C10" s="21">
+        <v>10</v>
+      </c>
+      <c r="D10" s="23">
+        <f t="shared" si="0"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="E10" s="25">
+        <f t="shared" si="1"/>
+        <v>3.0939750211478087E-2</v>
+      </c>
+      <c r="F10" s="25">
+        <f t="shared" si="2"/>
+        <v>0.1880404627556464</v>
+      </c>
+      <c r="G10" s="25">
+        <f t="shared" si="3"/>
+        <v>2.401961486777876E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" thickBot="1">
+      <c r="A11" s="21">
+        <v>10</v>
+      </c>
+      <c r="B11" s="21">
+        <v>90</v>
+      </c>
+      <c r="C11" s="21">
+        <v>6</v>
+      </c>
+      <c r="D11" s="23">
+        <f t="shared" si="0"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="E11" s="25">
+        <f t="shared" si="1"/>
+        <v>3.0939750211478087E-2</v>
+      </c>
+      <c r="F11" s="25">
+        <f t="shared" si="2"/>
+        <v>0.1880404627556464</v>
+      </c>
+      <c r="G11" s="25">
+        <f t="shared" si="3"/>
+        <v>2.401961486777876E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" thickBot="1">
+      <c r="A12" s="21">
+        <v>11</v>
+      </c>
+      <c r="B12" s="21">
+        <v>110</v>
+      </c>
+      <c r="C12" s="21">
+        <v>20</v>
+      </c>
+      <c r="D12" s="23">
+        <f t="shared" si="0"/>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="E12" s="25">
+        <f t="shared" si="1"/>
+        <v>2.7986057061488715E-2</v>
+      </c>
+      <c r="F12" s="25">
+        <f t="shared" si="2"/>
+        <v>0.17917938330567829</v>
+      </c>
+      <c r="G12" s="25">
+        <f t="shared" si="3"/>
+        <v>1.1263040936745988E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" thickBot="1">
+      <c r="A13" s="21">
+        <v>12</v>
+      </c>
+      <c r="B13" s="21">
+        <v>120</v>
+      </c>
+      <c r="C13" s="21">
+        <v>15</v>
+      </c>
+      <c r="D13" s="23">
+        <f t="shared" si="0"/>
+        <v>0.125</v>
+      </c>
+      <c r="E13" s="25">
+        <f t="shared" si="1"/>
+        <v>2.6794609669884981E-2</v>
+      </c>
+      <c r="F13" s="25">
+        <f t="shared" si="2"/>
+        <v>0.17560504113086708</v>
+      </c>
+      <c r="G13" s="25">
+        <f t="shared" si="3"/>
+        <v>1.483738311155719E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1">
+      <c r="A14" s="21">
+        <v>13</v>
+      </c>
+      <c r="B14" s="21">
+        <v>120</v>
+      </c>
+      <c r="C14" s="21">
+        <v>9</v>
+      </c>
+      <c r="D14" s="23">
+        <f t="shared" si="0"/>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="E14" s="25">
+        <f t="shared" si="1"/>
+        <v>2.6794609669884981E-2</v>
+      </c>
+      <c r="F14" s="25">
+        <f t="shared" si="2"/>
+        <v>0.17560504113086708</v>
+      </c>
+      <c r="G14" s="25">
+        <f t="shared" si="3"/>
+        <v>1.483738311155719E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" thickBot="1">
+      <c r="A15" s="21">
+        <v>14</v>
+      </c>
+      <c r="B15" s="21">
+        <v>120</v>
+      </c>
+      <c r="C15" s="21">
+        <v>8</v>
+      </c>
+      <c r="D15" s="23">
+        <f t="shared" si="0"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="E15" s="25">
+        <f t="shared" si="1"/>
+        <v>2.6794609669884981E-2</v>
+      </c>
+      <c r="F15" s="25">
+        <f t="shared" si="2"/>
+        <v>0.17560504113086708</v>
+      </c>
+      <c r="G15" s="25">
+        <f t="shared" si="3"/>
+        <v>1.483738311155719E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" thickBot="1">
+      <c r="A16" s="21">
+        <v>15</v>
+      </c>
+      <c r="B16" s="21">
+        <v>110</v>
+      </c>
+      <c r="C16" s="21">
+        <v>6</v>
+      </c>
+      <c r="D16" s="23">
+        <f t="shared" si="0"/>
+        <v>5.4545454545454543E-2</v>
+      </c>
+      <c r="E16" s="25">
+        <f t="shared" si="1"/>
+        <v>2.7986057061488715E-2</v>
+      </c>
+      <c r="F16" s="25">
+        <f t="shared" si="2"/>
+        <v>0.17917938330567829</v>
+      </c>
+      <c r="G16" s="25">
+        <f t="shared" si="3"/>
+        <v>1.1263040936745988E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1">
+      <c r="A17" s="21">
+        <v>16</v>
+      </c>
+      <c r="B17" s="21">
+        <v>80</v>
+      </c>
+      <c r="C17" s="21">
+        <v>8</v>
+      </c>
+      <c r="D17" s="23">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="E17" s="25">
+        <f t="shared" si="1"/>
+        <v>3.2816560774131108E-2</v>
+      </c>
+      <c r="F17" s="25">
+        <f t="shared" si="2"/>
+        <v>0.19367089444360547</v>
+      </c>
+      <c r="G17" s="25">
+        <f t="shared" si="3"/>
+        <v>-3.22847020118118E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1">
+      <c r="A18" s="21">
+        <v>17</v>
+      </c>
+      <c r="B18" s="21">
+        <v>80</v>
+      </c>
+      <c r="C18" s="21">
+        <v>10</v>
+      </c>
+      <c r="D18" s="23">
+        <f t="shared" si="0"/>
+        <v>0.125</v>
+      </c>
+      <c r="E18" s="25">
+        <f t="shared" si="1"/>
+        <v>3.2816560774131108E-2</v>
+      </c>
+      <c r="F18" s="25">
+        <f t="shared" si="2"/>
+        <v>0.19367089444360547</v>
+      </c>
+      <c r="G18" s="25">
+        <f t="shared" si="3"/>
+        <v>-3.22847020118118E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" thickBot="1">
+      <c r="A19" s="21">
+        <v>18</v>
+      </c>
+      <c r="B19" s="21">
+        <v>80</v>
+      </c>
+      <c r="C19" s="21">
+        <v>7</v>
+      </c>
+      <c r="D19" s="23">
+        <f t="shared" si="0"/>
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="E19" s="25">
+        <f t="shared" si="1"/>
+        <v>3.2816560774131108E-2</v>
+      </c>
+      <c r="F19" s="25">
+        <f t="shared" si="2"/>
+        <v>0.19367089444360547</v>
+      </c>
+      <c r="G19" s="25">
+        <f t="shared" si="3"/>
+        <v>-3.22847020118118E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" thickBot="1">
+      <c r="A20" s="21">
+        <v>19</v>
+      </c>
+      <c r="B20" s="21">
+        <v>90</v>
+      </c>
+      <c r="C20" s="21">
+        <v>5</v>
+      </c>
+      <c r="D20" s="23">
+        <f t="shared" si="0"/>
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="E20" s="25">
+        <f t="shared" si="1"/>
+        <v>3.0939750211478087E-2</v>
+      </c>
+      <c r="F20" s="25">
+        <f t="shared" si="2"/>
+        <v>0.1880404627556464</v>
+      </c>
+      <c r="G20" s="25">
+        <f t="shared" si="3"/>
+        <v>2.401961486777876E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" thickBot="1">
+      <c r="A21" s="21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="21">
+        <v>100</v>
+      </c>
+      <c r="C21" s="21">
+        <v>8</v>
+      </c>
+      <c r="D21" s="23">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+      <c r="E21" s="25">
+        <f t="shared" si="1"/>
+        <v>2.9352024271484114E-2</v>
+      </c>
+      <c r="F21" s="25">
+        <f t="shared" si="2"/>
+        <v>0.18327728493566448</v>
+      </c>
+      <c r="G21" s="25">
+        <f t="shared" si="3"/>
+        <v>7.165139306759799E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" thickBot="1">
+      <c r="A22" s="21">
+        <v>21</v>
+      </c>
+      <c r="B22" s="21">
+        <v>100</v>
+      </c>
+      <c r="C22" s="21">
+        <v>5</v>
+      </c>
+      <c r="D22" s="23">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="E22" s="25">
+        <f t="shared" si="1"/>
+        <v>2.9352024271484114E-2</v>
+      </c>
+      <c r="F22" s="25">
+        <f t="shared" si="2"/>
+        <v>0.18327728493566448</v>
+      </c>
+      <c r="G22" s="25">
+        <f t="shared" si="3"/>
+        <v>7.165139306759799E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" thickBot="1">
+      <c r="A23" s="21">
+        <v>22</v>
+      </c>
+      <c r="B23" s="21">
+        <v>100</v>
+      </c>
+      <c r="C23" s="21">
+        <v>8</v>
+      </c>
+      <c r="D23" s="23">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+      <c r="E23" s="25">
+        <f t="shared" si="1"/>
+        <v>2.9352024271484114E-2</v>
+      </c>
+      <c r="F23" s="25">
+        <f t="shared" si="2"/>
+        <v>0.18327728493566448</v>
+      </c>
+      <c r="G23" s="25">
+        <f t="shared" si="3"/>
+        <v>7.165139306759799E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" thickBot="1">
+      <c r="A24" s="21">
+        <v>23</v>
+      </c>
+      <c r="B24" s="21">
+        <v>100</v>
+      </c>
+      <c r="C24" s="21">
+        <v>10</v>
+      </c>
+      <c r="D24" s="23">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="E24" s="25">
+        <f t="shared" si="1"/>
+        <v>2.9352024271484114E-2</v>
+      </c>
+      <c r="F24" s="25">
+        <f t="shared" si="2"/>
+        <v>0.18327728493566448</v>
+      </c>
+      <c r="G24" s="25">
+        <f t="shared" si="3"/>
+        <v>7.165139306759799E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" thickBot="1">
+      <c r="A25" s="21">
+        <v>24</v>
+      </c>
+      <c r="B25" s="21">
+        <v>90</v>
+      </c>
+      <c r="C25" s="21">
+        <v>6</v>
+      </c>
+      <c r="D25" s="23">
+        <f t="shared" si="0"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="E25" s="25">
+        <f t="shared" si="1"/>
+        <v>3.0939750211478087E-2</v>
+      </c>
+      <c r="F25" s="25">
+        <f t="shared" si="2"/>
+        <v>0.1880404627556464</v>
+      </c>
+      <c r="G25" s="25">
+        <f t="shared" si="3"/>
+        <v>2.401961486777876E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" thickBot="1">
+      <c r="A26" s="21">
+        <v>25</v>
+      </c>
+      <c r="B26" s="21">
+        <v>90</v>
+      </c>
+      <c r="C26" s="21">
+        <v>9</v>
+      </c>
+      <c r="D26" s="23">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="E26" s="25">
+        <f t="shared" si="1"/>
+        <v>3.0939750211478087E-2</v>
+      </c>
+      <c r="F26" s="25">
+        <f t="shared" si="2"/>
+        <v>0.1880404627556464</v>
+      </c>
+      <c r="G26" s="25">
+        <f t="shared" si="3"/>
+        <v>2.401961486777876E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="42" thickBot="1">
+      <c r="A27" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="19">
+        <f>SUM(B2:B26)</f>
+        <v>2450</v>
+      </c>
+      <c r="C27" s="19">
+        <f>SUM(C2:C26)</f>
+        <v>234</v>
+      </c>
+      <c r="D27" s="24">
+        <f>SUM(D2:D26)</f>
+        <v>2.3805303030303033</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="D29" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="D30" s="25">
+        <f>AVERAGE(D2:D26)</f>
+        <v>9.5221212121212137E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="D31" s="25">
+        <f>1-D30</f>
+        <v>0.90477878787878785</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{806A18ED-75B3-4498-A4B1-048942345613}">
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="2" width="17.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="42" thickBot="1">
+      <c r="A1" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" thickBot="1">
+      <c r="A2" s="21">
+        <v>1</v>
+      </c>
+      <c r="B2" s="22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" thickBot="1">
+      <c r="A3" s="21">
+        <v>2</v>
+      </c>
+      <c r="B3" s="22">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15" thickBot="1">
+      <c r="A4" s="21">
+        <v>3</v>
+      </c>
+      <c r="B4" s="22">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" thickBot="1">
+      <c r="A5" s="21">
+        <v>4</v>
+      </c>
+      <c r="B5" s="22">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15" thickBot="1">
+      <c r="A6" s="21">
+        <v>5</v>
+      </c>
+      <c r="B6" s="22">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15" thickBot="1">
+      <c r="A7" s="21">
+        <v>6</v>
+      </c>
+      <c r="B7" s="22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15" thickBot="1">
+      <c r="A8" s="21">
+        <v>7</v>
+      </c>
+      <c r="B8" s="22">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15" thickBot="1">
+      <c r="A9" s="21">
+        <v>8</v>
+      </c>
+      <c r="B9" s="22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15" thickBot="1">
+      <c r="A10" s="21">
+        <v>9</v>
+      </c>
+      <c r="B10" s="22">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15" thickBot="1">
+      <c r="A11" s="21">
+        <v>10</v>
+      </c>
+      <c r="B11" s="22">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15" thickBot="1">
+      <c r="A12" s="21">
+        <v>11</v>
+      </c>
+      <c r="B12" s="22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15" thickBot="1">
+      <c r="A13" s="21">
+        <v>12</v>
+      </c>
+      <c r="B13" s="22">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15" thickBot="1">
+      <c r="A14" s="21">
+        <v>13</v>
+      </c>
+      <c r="B14" s="22">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15" thickBot="1">
+      <c r="A15" s="21">
+        <v>14</v>
+      </c>
+      <c r="B15" s="22">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15" thickBot="1">
+      <c r="A16" s="21">
+        <v>15</v>
+      </c>
+      <c r="B16" s="22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15" thickBot="1">
+      <c r="A17" s="21">
+        <v>16</v>
+      </c>
+      <c r="B17" s="22">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15" thickBot="1">
+      <c r="A18" s="21">
+        <v>17</v>
+      </c>
+      <c r="B18" s="22">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15" thickBot="1">
+      <c r="A19" s="21">
+        <v>18</v>
+      </c>
+      <c r="B19" s="22">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15" thickBot="1">
+      <c r="A20" s="21">
+        <v>19</v>
+      </c>
+      <c r="B20" s="22">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15" thickBot="1">
+      <c r="A21" s="21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="22">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15" thickBot="1">
+      <c r="A22" s="21">
+        <v>21</v>
+      </c>
+      <c r="B22" s="22">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15" thickBot="1">
+      <c r="A23" s="21">
+        <v>22</v>
+      </c>
+      <c r="B23" s="22">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15" thickBot="1">
+      <c r="A24" s="21">
+        <v>23</v>
+      </c>
+      <c r="B24" s="22">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15" thickBot="1">
+      <c r="A25" s="21">
+        <v>24</v>
+      </c>
+      <c r="B25" s="22">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15" thickBot="1">
+      <c r="A26" s="21">
+        <v>25</v>
+      </c>
+      <c r="B26" s="22">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15" thickBot="1">
+      <c r="A27" s="21">
+        <v>26</v>
+      </c>
+      <c r="B27" s="22">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9EBF900-428E-4144-BB26-C16DCDE15BED}">
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="4" width="22.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="28.2" thickBot="1">
+      <c r="A1" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" thickBot="1">
+      <c r="A2" s="21">
+        <v>1</v>
+      </c>
+      <c r="B2" s="21">
+        <v>100</v>
+      </c>
+      <c r="C2" s="21">
+        <v>18</v>
+      </c>
+      <c r="D2" s="22">
+        <v>0.18</v>
+      </c>
+      <c r="E2">
+        <f>SQRT($D$27/B2)</f>
+        <v>4.4181444068749041E-2</v>
+      </c>
+      <c r="F2" s="25">
+        <f>$D$27+(3*E2)</f>
+        <v>0.3277443322062471</v>
+      </c>
+      <c r="G2" s="25">
+        <f>$D$27-(3*E2)</f>
+        <v>6.2655667793752867E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" thickBot="1">
+      <c r="A3" s="21">
+        <v>2</v>
+      </c>
+      <c r="B3" s="21">
+        <v>100</v>
+      </c>
+      <c r="C3" s="21">
+        <v>22</v>
+      </c>
+      <c r="D3" s="22">
+        <v>0.22</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E26" si="0">SQRT($D$27/B3)</f>
+        <v>4.4181444068749041E-2</v>
+      </c>
+      <c r="F3" s="25">
+        <f t="shared" ref="F3:F26" si="1">$D$27+(3*E3)</f>
+        <v>0.3277443322062471</v>
+      </c>
+      <c r="G3" s="25">
+        <f t="shared" ref="G3:G26" si="2">$D$27-(3*E3)</f>
+        <v>6.2655667793752867E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" thickBot="1">
+      <c r="A4" s="21">
+        <v>3</v>
+      </c>
+      <c r="B4" s="21">
+        <v>90</v>
+      </c>
+      <c r="C4" s="21">
+        <v>15</v>
+      </c>
+      <c r="D4" s="22">
+        <v>0.17</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>4.6571331190861279E-2</v>
+      </c>
+      <c r="F4" s="25">
+        <f t="shared" si="1"/>
+        <v>0.33491399357258383</v>
+      </c>
+      <c r="G4" s="25">
+        <f t="shared" si="2"/>
+        <v>5.5486006427416135E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" thickBot="1">
+      <c r="A5" s="21">
+        <v>4</v>
+      </c>
+      <c r="B5" s="21">
+        <v>110</v>
+      </c>
+      <c r="C5" s="21">
+        <v>25</v>
+      </c>
+      <c r="D5" s="22">
+        <v>0.23</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>4.2125354058398776E-2</v>
+      </c>
+      <c r="F5" s="25">
+        <f t="shared" si="1"/>
+        <v>0.3215760621751963</v>
+      </c>
+      <c r="G5" s="25">
+        <f t="shared" si="2"/>
+        <v>6.8823937824803672E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickBot="1">
+      <c r="A6" s="21">
+        <v>5</v>
+      </c>
+      <c r="B6" s="21">
+        <v>100</v>
+      </c>
+      <c r="C6" s="21">
+        <v>12</v>
+      </c>
+      <c r="D6" s="22">
+        <v>0.12</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>4.4181444068749041E-2</v>
+      </c>
+      <c r="F6" s="25">
+        <f t="shared" si="1"/>
+        <v>0.3277443322062471</v>
+      </c>
+      <c r="G6" s="25">
+        <f t="shared" si="2"/>
+        <v>6.2655667793752867E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" thickBot="1">
+      <c r="A7" s="21">
+        <v>6</v>
+      </c>
+      <c r="B7" s="21">
+        <v>100</v>
+      </c>
+      <c r="C7" s="21">
+        <v>19</v>
+      </c>
+      <c r="D7" s="22">
+        <v>0.19</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>4.4181444068749041E-2</v>
+      </c>
+      <c r="F7" s="25">
+        <f t="shared" si="1"/>
+        <v>0.3277443322062471</v>
+      </c>
+      <c r="G7" s="25">
+        <f t="shared" si="2"/>
+        <v>6.2655667793752867E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" thickBot="1">
+      <c r="A8" s="21">
+        <v>7</v>
+      </c>
+      <c r="B8" s="21">
+        <v>95</v>
+      </c>
+      <c r="C8" s="21">
+        <v>20</v>
+      </c>
+      <c r="D8" s="22">
+        <v>0.21</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>4.5329205178397544E-2</v>
+      </c>
+      <c r="F8" s="25">
+        <f t="shared" si="1"/>
+        <v>0.3311876155351926</v>
+      </c>
+      <c r="G8" s="25">
+        <f t="shared" si="2"/>
+        <v>5.9212384464807366E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" thickBot="1">
+      <c r="A9" s="21">
+        <v>8</v>
+      </c>
+      <c r="B9" s="21">
+        <v>105</v>
+      </c>
+      <c r="C9" s="21">
+        <v>24</v>
+      </c>
+      <c r="D9" s="22">
+        <v>0.23</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>4.3116674489663727E-2</v>
+      </c>
+      <c r="F9" s="25">
+        <f t="shared" si="1"/>
+        <v>0.3245500234689912</v>
+      </c>
+      <c r="G9" s="25">
+        <f t="shared" si="2"/>
+        <v>6.5849976531008797E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" thickBot="1">
+      <c r="A10" s="21">
+        <v>9</v>
+      </c>
+      <c r="B10" s="21">
+        <v>100</v>
+      </c>
+      <c r="C10" s="21">
+        <v>30</v>
+      </c>
+      <c r="D10" s="22">
+        <v>0.3</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>4.4181444068749041E-2</v>
+      </c>
+      <c r="F10" s="25">
+        <f t="shared" si="1"/>
+        <v>0.3277443322062471</v>
+      </c>
+      <c r="G10" s="25">
+        <f t="shared" si="2"/>
+        <v>6.2655667793752867E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" thickBot="1">
+      <c r="A11" s="21">
+        <v>10</v>
+      </c>
+      <c r="B11" s="21">
+        <v>100</v>
+      </c>
+      <c r="C11" s="21">
+        <v>17</v>
+      </c>
+      <c r="D11" s="22">
+        <v>0.17</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>4.4181444068749041E-2</v>
+      </c>
+      <c r="F11" s="25">
+        <f t="shared" si="1"/>
+        <v>0.3277443322062471</v>
+      </c>
+      <c r="G11" s="25">
+        <f t="shared" si="2"/>
+        <v>6.2655667793752867E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" thickBot="1">
+      <c r="A12" s="21">
+        <v>11</v>
+      </c>
+      <c r="B12" s="21">
+        <v>90</v>
+      </c>
+      <c r="C12" s="21">
+        <v>14</v>
+      </c>
+      <c r="D12" s="22">
+        <v>0.16</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>4.6571331190861279E-2</v>
+      </c>
+      <c r="F12" s="25">
+        <f t="shared" si="1"/>
+        <v>0.33491399357258383</v>
+      </c>
+      <c r="G12" s="25">
+        <f t="shared" si="2"/>
+        <v>5.5486006427416135E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" thickBot="1">
+      <c r="A13" s="21">
+        <v>12</v>
+      </c>
+      <c r="B13" s="21">
+        <v>110</v>
+      </c>
+      <c r="C13" s="21">
+        <v>22</v>
+      </c>
+      <c r="D13" s="22">
+        <v>0.2</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>4.2125354058398776E-2</v>
+      </c>
+      <c r="F13" s="25">
+        <f t="shared" si="1"/>
+        <v>0.3215760621751963</v>
+      </c>
+      <c r="G13" s="25">
+        <f t="shared" si="2"/>
+        <v>6.8823937824803672E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1">
+      <c r="A14" s="21">
+        <v>13</v>
+      </c>
+      <c r="B14" s="21">
+        <v>100</v>
+      </c>
+      <c r="C14" s="21">
+        <v>16</v>
+      </c>
+      <c r="D14" s="22">
+        <v>0.16</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>4.4181444068749041E-2</v>
+      </c>
+      <c r="F14" s="25">
+        <f t="shared" si="1"/>
+        <v>0.3277443322062471</v>
+      </c>
+      <c r="G14" s="25">
+        <f t="shared" si="2"/>
+        <v>6.2655667793752867E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" thickBot="1">
+      <c r="A15" s="21">
+        <v>14</v>
+      </c>
+      <c r="B15" s="21">
+        <v>100</v>
+      </c>
+      <c r="C15" s="21">
+        <v>21</v>
+      </c>
+      <c r="D15" s="22">
+        <v>0.21</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>4.4181444068749041E-2</v>
+      </c>
+      <c r="F15" s="25">
+        <f t="shared" si="1"/>
+        <v>0.3277443322062471</v>
+      </c>
+      <c r="G15" s="25">
+        <f t="shared" si="2"/>
+        <v>6.2655667793752867E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" thickBot="1">
+      <c r="A16" s="21">
+        <v>15</v>
+      </c>
+      <c r="B16" s="21">
+        <v>95</v>
+      </c>
+      <c r="C16" s="21">
+        <v>18</v>
+      </c>
+      <c r="D16" s="22">
+        <v>0.19</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>4.5329205178397544E-2</v>
+      </c>
+      <c r="F16" s="25">
+        <f t="shared" si="1"/>
+        <v>0.3311876155351926</v>
+      </c>
+      <c r="G16" s="25">
+        <f t="shared" si="2"/>
+        <v>5.9212384464807366E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1">
+      <c r="A17" s="21">
+        <v>16</v>
+      </c>
+      <c r="B17" s="21">
+        <v>105</v>
+      </c>
+      <c r="C17" s="21">
+        <v>26</v>
+      </c>
+      <c r="D17" s="22">
+        <v>0.25</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>4.3116674489663727E-2</v>
+      </c>
+      <c r="F17" s="25">
+        <f t="shared" si="1"/>
+        <v>0.3245500234689912</v>
+      </c>
+      <c r="G17" s="25">
+        <f t="shared" si="2"/>
+        <v>6.5849976531008797E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1">
+      <c r="A18" s="21">
+        <v>17</v>
+      </c>
+      <c r="B18" s="21">
+        <v>100</v>
+      </c>
+      <c r="C18" s="21">
+        <v>19</v>
+      </c>
+      <c r="D18" s="22">
+        <v>0.19</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="0"/>
+        <v>4.4181444068749041E-2</v>
+      </c>
+      <c r="F18" s="25">
+        <f t="shared" si="1"/>
+        <v>0.3277443322062471</v>
+      </c>
+      <c r="G18" s="25">
+        <f t="shared" si="2"/>
+        <v>6.2655667793752867E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" thickBot="1">
+      <c r="A19" s="21">
+        <v>18</v>
+      </c>
+      <c r="B19" s="21">
+        <v>100</v>
+      </c>
+      <c r="C19" s="21">
+        <v>13</v>
+      </c>
+      <c r="D19" s="22">
+        <v>0.13</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="0"/>
+        <v>4.4181444068749041E-2</v>
+      </c>
+      <c r="F19" s="25">
+        <f t="shared" si="1"/>
+        <v>0.3277443322062471</v>
+      </c>
+      <c r="G19" s="25">
+        <f t="shared" si="2"/>
+        <v>6.2655667793752867E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" thickBot="1">
+      <c r="A20" s="21">
+        <v>19</v>
+      </c>
+      <c r="B20" s="21">
+        <v>90</v>
+      </c>
+      <c r="C20" s="21">
+        <v>12</v>
+      </c>
+      <c r="D20" s="22">
+        <v>0.13</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="0"/>
+        <v>4.6571331190861279E-2</v>
+      </c>
+      <c r="F20" s="25">
+        <f t="shared" si="1"/>
+        <v>0.33491399357258383</v>
+      </c>
+      <c r="G20" s="25">
+        <f t="shared" si="2"/>
+        <v>5.5486006427416135E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" thickBot="1">
+      <c r="A21" s="21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="21">
+        <v>110</v>
+      </c>
+      <c r="C21" s="21">
+        <v>35</v>
+      </c>
+      <c r="D21" s="22">
+        <v>0.32</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="0"/>
+        <v>4.2125354058398776E-2</v>
+      </c>
+      <c r="F21" s="25">
+        <f t="shared" si="1"/>
+        <v>0.3215760621751963</v>
+      </c>
+      <c r="G21" s="25">
+        <f t="shared" si="2"/>
+        <v>6.8823937824803672E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" thickBot="1">
+      <c r="A22" s="21">
+        <v>21</v>
+      </c>
+      <c r="B22" s="21">
+        <v>100</v>
+      </c>
+      <c r="C22" s="21">
+        <v>20</v>
+      </c>
+      <c r="D22" s="22">
+        <v>0.2</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="0"/>
+        <v>4.4181444068749041E-2</v>
+      </c>
+      <c r="F22" s="25">
+        <f t="shared" si="1"/>
+        <v>0.3277443322062471</v>
+      </c>
+      <c r="G22" s="25">
+        <f t="shared" si="2"/>
+        <v>6.2655667793752867E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" thickBot="1">
+      <c r="A23" s="21">
+        <v>22</v>
+      </c>
+      <c r="B23" s="21">
+        <v>100</v>
+      </c>
+      <c r="C23" s="21">
+        <v>18</v>
+      </c>
+      <c r="D23" s="22">
+        <v>0.18</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="0"/>
+        <v>4.4181444068749041E-2</v>
+      </c>
+      <c r="F23" s="25">
+        <f t="shared" si="1"/>
+        <v>0.3277443322062471</v>
+      </c>
+      <c r="G23" s="25">
+        <f t="shared" si="2"/>
+        <v>6.2655667793752867E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" thickBot="1">
+      <c r="A24" s="21">
+        <v>23</v>
+      </c>
+      <c r="B24" s="21">
+        <v>95</v>
+      </c>
+      <c r="C24" s="21">
+        <v>15</v>
+      </c>
+      <c r="D24" s="22">
+        <v>0.16</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="0"/>
+        <v>4.5329205178397544E-2</v>
+      </c>
+      <c r="F24" s="25">
+        <f t="shared" si="1"/>
+        <v>0.3311876155351926</v>
+      </c>
+      <c r="G24" s="25">
+        <f t="shared" si="2"/>
+        <v>5.9212384464807366E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" thickBot="1">
+      <c r="A25" s="21">
+        <v>24</v>
+      </c>
+      <c r="B25" s="21">
+        <v>105</v>
+      </c>
+      <c r="C25" s="21">
+        <v>22</v>
+      </c>
+      <c r="D25" s="22">
+        <v>0.21</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="0"/>
+        <v>4.3116674489663727E-2</v>
+      </c>
+      <c r="F25" s="25">
+        <f t="shared" si="1"/>
+        <v>0.3245500234689912</v>
+      </c>
+      <c r="G25" s="25">
+        <f t="shared" si="2"/>
+        <v>6.5849976531008797E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" thickBot="1">
+      <c r="A26" s="21">
+        <v>25</v>
+      </c>
+      <c r="B26" s="21">
+        <v>100</v>
+      </c>
+      <c r="C26" s="21">
+        <v>17</v>
+      </c>
+      <c r="D26" s="22">
+        <v>0.17</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="0"/>
+        <v>4.4181444068749041E-2</v>
+      </c>
+      <c r="F26" s="25">
+        <f t="shared" si="1"/>
+        <v>0.3277443322062471</v>
+      </c>
+      <c r="G26" s="25">
+        <f t="shared" si="2"/>
+        <v>6.2655667793752867E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="D27">
+        <f>AVERAGE(D2:D26)</f>
+        <v>0.19519999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Sample dataxlsx.xlsx
+++ b/Sample dataxlsx.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\S2 Smart Manufacturing and Applied information science\2 Semester\Advance Statistical Quality Control\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\S2 Smart Manufacturing and Applied information science\2 Semester\Advance Statistical Quality Control\project control chart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A8B4AD-8B50-4534-87AA-F0F9DCCAC02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D96DDB-42C0-435A-8DB0-E06E6AB82760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{E9B4DBE7-7145-4880-9E7C-D6384306006F}"/>
+    <workbookView xWindow="0" yWindow="1560" windowWidth="15360" windowHeight="8856" activeTab="1" xr2:uid="{E9B4DBE7-7145-4880-9E7C-D6384306006F}"/>
   </bookViews>
   <sheets>
     <sheet name="CUSUM Chart" sheetId="3" r:id="rId1"/>
@@ -279,7 +279,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -499,12 +499,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
@@ -523,9 +517,15 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11302,16 +11302,16 @@
       </c>
     </row>
     <row r="56" spans="1:24">
-      <c r="D56" s="17" t="s">
+      <c r="D56" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="E56" s="17"/>
-      <c r="F56" s="17"/>
-      <c r="G56" s="18" t="s">
+      <c r="E56" s="25"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="H56" s="18"/>
-      <c r="I56" s="18"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="26"/>
     </row>
     <row r="57" spans="1:24">
       <c r="A57" s="14" t="s">
@@ -11964,1097 +11964,1097 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="42" thickBot="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="18" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" thickBot="1">
-      <c r="A2" s="21">
+      <c r="A2" s="19">
         <v>1</v>
       </c>
-      <c r="B2" s="21">
+      <c r="B2" s="19">
         <v>12</v>
       </c>
-      <c r="C2" s="22">
+      <c r="C2" s="20">
         <v>0.24</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" thickBot="1">
-      <c r="A3" s="21">
+      <c r="A3" s="19">
         <v>2</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="19">
         <v>15</v>
       </c>
-      <c r="C3" s="22">
+      <c r="C3" s="20">
         <v>0.3</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" thickBot="1">
-      <c r="A4" s="21">
+      <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="19">
         <v>8</v>
       </c>
-      <c r="C4" s="22">
+      <c r="C4" s="20">
         <v>0.16</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" thickBot="1">
-      <c r="A5" s="21">
+      <c r="A5" s="19">
         <v>4</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="19">
         <v>10</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="20">
         <v>0.2</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" thickBot="1">
-      <c r="A6" s="21">
+      <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="19">
         <v>4</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="20">
         <v>0.08</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" thickBot="1">
-      <c r="A7" s="21">
+      <c r="A7" s="19">
         <v>6</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="19">
         <v>7</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="20">
         <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" thickBot="1">
-      <c r="A8" s="21">
+      <c r="A8" s="19">
         <v>7</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="19">
         <v>16</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="20">
         <v>0.32</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" thickBot="1">
-      <c r="A9" s="21">
+      <c r="A9" s="19">
         <v>8</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="19">
         <v>9</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="20">
         <v>0.18</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" thickBot="1">
-      <c r="A10" s="21">
+      <c r="A10" s="19">
         <v>9</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="19">
         <v>14</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="20">
         <v>0.28000000000000003</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" thickBot="1">
-      <c r="A11" s="21">
+      <c r="A11" s="19">
         <v>10</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="19">
         <v>10</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="20">
         <v>0.2</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" thickBot="1">
-      <c r="A12" s="21">
+      <c r="A12" s="19">
         <v>11</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="19">
         <v>5</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="20">
         <v>0.1</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" thickBot="1">
-      <c r="A13" s="21">
+      <c r="A13" s="19">
         <v>12</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="19">
         <v>6</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="20">
         <v>0.12</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" thickBot="1">
-      <c r="A14" s="21">
+      <c r="A14" s="19">
         <v>13</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="19">
         <v>17</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="20">
         <v>0.34</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" thickBot="1">
-      <c r="A15" s="21">
+      <c r="A15" s="19">
         <v>14</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="19">
         <v>12</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="20">
         <v>0.24</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" thickBot="1">
-      <c r="A16" s="21">
+      <c r="A16" s="19">
         <v>15</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="19">
         <v>22</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="20">
         <v>0.44</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" thickBot="1">
-      <c r="A17" s="21">
+      <c r="A17" s="19">
         <v>16</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="19">
         <v>8</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="20">
         <v>0.16</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" thickBot="1">
-      <c r="A18" s="21">
+      <c r="A18" s="19">
         <v>17</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="19">
         <v>10</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="20">
         <v>0.2</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" thickBot="1">
-      <c r="A19" s="21">
+      <c r="A19" s="19">
         <v>18</v>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="19">
         <v>5</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="20">
         <v>0.1</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" thickBot="1">
-      <c r="A20" s="21">
+      <c r="A20" s="19">
         <v>19</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="19">
         <v>13</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="20">
         <v>0.26</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" thickBot="1">
-      <c r="A21" s="21">
+      <c r="A21" s="19">
         <v>20</v>
       </c>
-      <c r="B21" s="21">
+      <c r="B21" s="19">
         <v>11</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="20">
         <v>0.22</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" thickBot="1">
-      <c r="A22" s="21">
+      <c r="A22" s="19">
         <v>21</v>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="19">
         <v>20</v>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="20">
         <v>0.4</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15" thickBot="1">
-      <c r="A23" s="21">
+      <c r="A23" s="19">
         <v>22</v>
       </c>
-      <c r="B23" s="21">
+      <c r="B23" s="19">
         <v>18</v>
       </c>
-      <c r="C23" s="22">
+      <c r="C23" s="20">
         <v>0.36</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" thickBot="1">
-      <c r="A24" s="21">
+      <c r="A24" s="19">
         <v>23</v>
       </c>
-      <c r="B24" s="21">
+      <c r="B24" s="19">
         <v>24</v>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="20">
         <v>0.48</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" thickBot="1">
-      <c r="A25" s="21">
+      <c r="A25" s="19">
         <v>24</v>
       </c>
-      <c r="B25" s="21">
+      <c r="B25" s="19">
         <v>15</v>
       </c>
-      <c r="C25" s="22">
+      <c r="C25" s="20">
         <v>0.3</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15" thickBot="1">
-      <c r="A26" s="21">
+      <c r="A26" s="19">
         <v>25</v>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="19">
         <v>9</v>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="20">
         <v>0.18</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15" thickBot="1">
-      <c r="A27" s="21">
+      <c r="A27" s="19">
         <v>26</v>
       </c>
-      <c r="B27" s="21">
+      <c r="B27" s="19">
         <v>12</v>
       </c>
-      <c r="C27" s="22">
+      <c r="C27" s="20">
         <v>0.24</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15" thickBot="1">
-      <c r="A28" s="21">
+      <c r="A28" s="19">
         <v>27</v>
       </c>
-      <c r="B28" s="21">
+      <c r="B28" s="19">
         <v>7</v>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="20">
         <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" thickBot="1">
-      <c r="A29" s="21">
+      <c r="A29" s="19">
         <v>28</v>
       </c>
-      <c r="B29" s="21">
+      <c r="B29" s="19">
         <v>13</v>
       </c>
-      <c r="C29" s="22">
+      <c r="C29" s="20">
         <v>0.26</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15" thickBot="1">
-      <c r="A30" s="21">
+      <c r="A30" s="19">
         <v>29</v>
       </c>
-      <c r="B30" s="21">
+      <c r="B30" s="19">
         <v>9</v>
       </c>
-      <c r="C30" s="22">
+      <c r="C30" s="20">
         <v>0.18</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15" thickBot="1">
-      <c r="A31" s="21">
+      <c r="A31" s="19">
         <v>30</v>
       </c>
-      <c r="B31" s="21">
+      <c r="B31" s="19">
         <v>6</v>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="20">
         <v>0.12</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="42" thickBot="1">
-      <c r="A32" s="19" t="s">
+    <row r="32" spans="1:3" ht="15" thickBot="1">
+      <c r="A32" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B32" s="19">
+      <c r="B32" s="17">
         <f>SUM(B2:B31)</f>
         <v>347</v>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="18">
         <f>AVERAGE(C2:C31)</f>
         <v>0.23133333333333334</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" thickBot="1"/>
     <row r="35" spans="1:3" ht="42" thickBot="1">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C35" s="20" t="s">
+      <c r="C35" s="18" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15" thickBot="1">
-      <c r="A36" s="21">
+      <c r="A36" s="19">
         <v>31</v>
       </c>
-      <c r="B36" s="21">
+      <c r="B36" s="19">
         <v>9</v>
       </c>
-      <c r="C36" s="22">
+      <c r="C36" s="20">
         <v>0.18</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15" thickBot="1">
-      <c r="A37" s="21">
+      <c r="A37" s="19">
         <v>32</v>
       </c>
-      <c r="B37" s="21">
+      <c r="B37" s="19">
         <v>6</v>
       </c>
-      <c r="C37" s="22">
+      <c r="C37" s="20">
         <v>0.12</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15" thickBot="1">
-      <c r="A38" s="21">
+      <c r="A38" s="19">
         <v>33</v>
       </c>
-      <c r="B38" s="21">
+      <c r="B38" s="19">
         <v>12</v>
       </c>
-      <c r="C38" s="22">
+      <c r="C38" s="20">
         <v>0.24</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15" thickBot="1">
-      <c r="A39" s="21">
+      <c r="A39" s="19">
         <v>34</v>
       </c>
-      <c r="B39" s="21">
+      <c r="B39" s="19">
         <v>5</v>
       </c>
-      <c r="C39" s="22">
+      <c r="C39" s="20">
         <v>0.1</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15" thickBot="1">
-      <c r="A40" s="21">
+      <c r="A40" s="19">
         <v>35</v>
       </c>
-      <c r="B40" s="21">
+      <c r="B40" s="19">
         <v>6</v>
       </c>
-      <c r="C40" s="22">
+      <c r="C40" s="20">
         <v>0.12</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15" thickBot="1">
-      <c r="A41" s="21">
+      <c r="A41" s="19">
         <v>36</v>
       </c>
-      <c r="B41" s="21">
+      <c r="B41" s="19">
         <v>4</v>
       </c>
-      <c r="C41" s="22">
+      <c r="C41" s="20">
         <v>0.08</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15" thickBot="1">
-      <c r="A42" s="21">
+      <c r="A42" s="19">
         <v>37</v>
       </c>
-      <c r="B42" s="21">
+      <c r="B42" s="19">
         <v>6</v>
       </c>
-      <c r="C42" s="22">
+      <c r="C42" s="20">
         <v>0.12</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15" thickBot="1">
-      <c r="A43" s="21">
+      <c r="A43" s="19">
         <v>38</v>
       </c>
-      <c r="B43" s="21">
+      <c r="B43" s="19">
         <v>3</v>
       </c>
-      <c r="C43" s="22">
+      <c r="C43" s="20">
         <v>0.06</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15" thickBot="1">
-      <c r="A44" s="21">
+      <c r="A44" s="19">
         <v>39</v>
       </c>
-      <c r="B44" s="21">
+      <c r="B44" s="19">
         <v>7</v>
       </c>
-      <c r="C44" s="22">
+      <c r="C44" s="20">
         <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15" thickBot="1">
-      <c r="A45" s="21">
+      <c r="A45" s="19">
         <v>40</v>
       </c>
-      <c r="B45" s="21">
+      <c r="B45" s="19">
         <v>6</v>
       </c>
-      <c r="C45" s="22">
+      <c r="C45" s="20">
         <v>0.12</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15" thickBot="1">
-      <c r="A46" s="21">
+      <c r="A46" s="19">
         <v>41</v>
       </c>
-      <c r="B46" s="21">
+      <c r="B46" s="19">
         <v>2</v>
       </c>
-      <c r="C46" s="22">
+      <c r="C46" s="20">
         <v>0.04</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="15" thickBot="1">
-      <c r="A47" s="21">
+      <c r="A47" s="19">
         <v>42</v>
       </c>
-      <c r="B47" s="21">
+      <c r="B47" s="19">
         <v>4</v>
       </c>
-      <c r="C47" s="22">
+      <c r="C47" s="20">
         <v>0.08</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="15" thickBot="1">
-      <c r="A48" s="21">
+      <c r="A48" s="19">
         <v>43</v>
       </c>
-      <c r="B48" s="21">
+      <c r="B48" s="19">
         <v>3</v>
       </c>
-      <c r="C48" s="22">
+      <c r="C48" s="20">
         <v>0.06</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="15" thickBot="1">
-      <c r="A49" s="21">
+      <c r="A49" s="19">
         <v>44</v>
       </c>
-      <c r="B49" s="21">
+      <c r="B49" s="19">
         <v>6</v>
       </c>
-      <c r="C49" s="22">
+      <c r="C49" s="20">
         <v>0.12</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="15" thickBot="1">
-      <c r="A50" s="21">
+      <c r="A50" s="19">
         <v>45</v>
       </c>
-      <c r="B50" s="21">
+      <c r="B50" s="19">
         <v>5</v>
       </c>
-      <c r="C50" s="22">
+      <c r="C50" s="20">
         <v>0.1</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="15" thickBot="1">
-      <c r="A51" s="21">
+      <c r="A51" s="19">
         <v>46</v>
       </c>
-      <c r="B51" s="21">
+      <c r="B51" s="19">
         <v>4</v>
       </c>
-      <c r="C51" s="22">
+      <c r="C51" s="20">
         <v>0.08</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="15" thickBot="1">
-      <c r="A52" s="21">
+      <c r="A52" s="19">
         <v>47</v>
       </c>
-      <c r="B52" s="21">
+      <c r="B52" s="19">
         <v>8</v>
       </c>
-      <c r="C52" s="22">
+      <c r="C52" s="20">
         <v>0.16</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="15" thickBot="1">
-      <c r="A53" s="21">
+      <c r="A53" s="19">
         <v>48</v>
       </c>
-      <c r="B53" s="21">
+      <c r="B53" s="19">
         <v>5</v>
       </c>
-      <c r="C53" s="22">
+      <c r="C53" s="20">
         <v>0.1</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="15" thickBot="1">
-      <c r="A54" s="21">
+      <c r="A54" s="19">
         <v>49</v>
       </c>
-      <c r="B54" s="21">
+      <c r="B54" s="19">
         <v>6</v>
       </c>
-      <c r="C54" s="22">
+      <c r="C54" s="20">
         <v>0.12</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="15" thickBot="1">
-      <c r="A55" s="21">
+      <c r="A55" s="19">
         <v>50</v>
       </c>
-      <c r="B55" s="21">
+      <c r="B55" s="19">
         <v>7</v>
       </c>
-      <c r="C55" s="22">
+      <c r="C55" s="20">
         <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="15" thickBot="1">
-      <c r="A56" s="21">
+      <c r="A56" s="19">
         <v>51</v>
       </c>
-      <c r="B56" s="21">
+      <c r="B56" s="19">
         <v>5</v>
       </c>
-      <c r="C56" s="22">
+      <c r="C56" s="20">
         <v>0.1</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="15" thickBot="1">
-      <c r="A57" s="21">
+      <c r="A57" s="19">
         <v>52</v>
       </c>
-      <c r="B57" s="21">
+      <c r="B57" s="19">
         <v>6</v>
       </c>
-      <c r="C57" s="22">
+      <c r="C57" s="20">
         <v>0.12</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="15" thickBot="1">
-      <c r="A58" s="21">
+      <c r="A58" s="19">
         <v>53</v>
       </c>
-      <c r="B58" s="21">
+      <c r="B58" s="19">
         <v>3</v>
       </c>
-      <c r="C58" s="22">
+      <c r="C58" s="20">
         <v>0.06</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="15" thickBot="1">
-      <c r="A59" s="21">
+      <c r="A59" s="19">
         <v>54</v>
       </c>
-      <c r="B59" s="21">
+      <c r="B59" s="19">
         <v>5</v>
       </c>
-      <c r="C59" s="22">
+      <c r="C59" s="20">
         <v>0.1</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="15" thickBot="1">
-      <c r="A60" s="19" t="s">
+      <c r="A60" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B60" s="19">
+      <c r="B60" s="17">
         <f>SUM(B36:B59)</f>
         <v>133</v>
       </c>
-      <c r="C60" s="20">
+      <c r="C60" s="18">
         <f>AVERAGE(C36:C59)</f>
         <v>0.11083333333333338</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="15" thickBot="1"/>
     <row r="63" spans="1:3" ht="42" thickBot="1">
-      <c r="A63" s="19" t="s">
+      <c r="A63" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B63" s="19" t="s">
+      <c r="B63" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C63" s="20" t="s">
+      <c r="C63" s="18" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="15" thickBot="1">
-      <c r="A64" s="21">
+      <c r="A64" s="19">
         <v>55</v>
       </c>
-      <c r="B64" s="21">
+      <c r="B64" s="19">
         <v>8</v>
       </c>
-      <c r="C64" s="22">
+      <c r="C64" s="20">
         <v>0.16</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="15" thickBot="1">
-      <c r="A65" s="21">
+      <c r="A65" s="19">
         <v>56</v>
       </c>
-      <c r="B65" s="21">
+      <c r="B65" s="19">
         <v>7</v>
       </c>
-      <c r="C65" s="22">
+      <c r="C65" s="20">
         <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="15" thickBot="1">
-      <c r="A66" s="21">
+      <c r="A66" s="19">
         <v>57</v>
       </c>
-      <c r="B66" s="21">
+      <c r="B66" s="19">
         <v>5</v>
       </c>
-      <c r="C66" s="22">
+      <c r="C66" s="20">
         <v>0.1</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="15" thickBot="1">
-      <c r="A67" s="21">
+      <c r="A67" s="19">
         <v>58</v>
       </c>
-      <c r="B67" s="21">
+      <c r="B67" s="19">
         <v>6</v>
       </c>
-      <c r="C67" s="22">
+      <c r="C67" s="20">
         <v>0.12</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="15" thickBot="1">
-      <c r="A68" s="21">
+      <c r="A68" s="19">
         <v>59</v>
       </c>
-      <c r="B68" s="21">
+      <c r="B68" s="19">
         <v>4</v>
       </c>
-      <c r="C68" s="22">
+      <c r="C68" s="20">
         <v>0.08</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="15" thickBot="1">
-      <c r="A69" s="21">
+      <c r="A69" s="19">
         <v>60</v>
       </c>
-      <c r="B69" s="21">
+      <c r="B69" s="19">
         <v>5</v>
       </c>
-      <c r="C69" s="22">
+      <c r="C69" s="20">
         <v>0.1</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="15" thickBot="1">
-      <c r="A70" s="21">
+      <c r="A70" s="19">
         <v>61</v>
       </c>
-      <c r="B70" s="21">
+      <c r="B70" s="19">
         <v>2</v>
       </c>
-      <c r="C70" s="22">
+      <c r="C70" s="20">
         <v>0.04</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="15" thickBot="1">
-      <c r="A71" s="21">
+      <c r="A71" s="19">
         <v>62</v>
       </c>
-      <c r="B71" s="21">
+      <c r="B71" s="19">
         <v>3</v>
       </c>
-      <c r="C71" s="22">
+      <c r="C71" s="20">
         <v>0.06</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="15" thickBot="1">
-      <c r="A72" s="21">
+      <c r="A72" s="19">
         <v>63</v>
       </c>
-      <c r="B72" s="21">
+      <c r="B72" s="19">
         <v>4</v>
       </c>
-      <c r="C72" s="22">
+      <c r="C72" s="20">
         <v>0.08</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="15" thickBot="1">
-      <c r="A73" s="21">
+      <c r="A73" s="19">
         <v>64</v>
       </c>
-      <c r="B73" s="21">
+      <c r="B73" s="19">
         <v>7</v>
       </c>
-      <c r="C73" s="22">
+      <c r="C73" s="20">
         <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="15" thickBot="1">
-      <c r="A74" s="21">
+      <c r="A74" s="19">
         <v>65</v>
       </c>
-      <c r="B74" s="21">
+      <c r="B74" s="19">
         <v>6</v>
       </c>
-      <c r="C74" s="22">
+      <c r="C74" s="20">
         <v>0.12</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="15" thickBot="1">
-      <c r="A75" s="21">
+      <c r="A75" s="19">
         <v>66</v>
       </c>
-      <c r="B75" s="21">
+      <c r="B75" s="19">
         <v>5</v>
       </c>
-      <c r="C75" s="22">
+      <c r="C75" s="20">
         <v>0.1</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="15" thickBot="1">
-      <c r="A76" s="21">
+      <c r="A76" s="19">
         <v>67</v>
       </c>
-      <c r="B76" s="21">
+      <c r="B76" s="19">
         <v>5</v>
       </c>
-      <c r="C76" s="22">
+      <c r="C76" s="20">
         <v>0.1</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="15" thickBot="1">
-      <c r="A77" s="21">
+      <c r="A77" s="19">
         <v>68</v>
       </c>
-      <c r="B77" s="21">
+      <c r="B77" s="19">
         <v>3</v>
       </c>
-      <c r="C77" s="22">
+      <c r="C77" s="20">
         <v>0.06</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15" thickBot="1">
-      <c r="A78" s="21">
+      <c r="A78" s="19">
         <v>69</v>
       </c>
-      <c r="B78" s="21">
+      <c r="B78" s="19">
         <v>7</v>
       </c>
-      <c r="C78" s="22">
+      <c r="C78" s="20">
         <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="15" thickBot="1">
-      <c r="A79" s="21">
+      <c r="A79" s="19">
         <v>70</v>
       </c>
-      <c r="B79" s="21">
+      <c r="B79" s="19">
         <v>9</v>
       </c>
-      <c r="C79" s="22">
+      <c r="C79" s="20">
         <v>0.18</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="15" thickBot="1">
-      <c r="A80" s="21">
+      <c r="A80" s="19">
         <v>71</v>
       </c>
-      <c r="B80" s="21">
+      <c r="B80" s="19">
         <v>6</v>
       </c>
-      <c r="C80" s="22">
+      <c r="C80" s="20">
         <v>0.12</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="15" thickBot="1">
-      <c r="A81" s="21">
+      <c r="A81" s="19">
         <v>72</v>
       </c>
-      <c r="B81" s="21">
+      <c r="B81" s="19">
         <v>10</v>
       </c>
-      <c r="C81" s="22">
+      <c r="C81" s="20">
         <v>0.2</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="15" thickBot="1">
-      <c r="A82" s="21">
+      <c r="A82" s="19">
         <v>73</v>
       </c>
-      <c r="B82" s="21">
+      <c r="B82" s="19">
         <v>4</v>
       </c>
-      <c r="C82" s="22">
+      <c r="C82" s="20">
         <v>0.08</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="15" thickBot="1">
-      <c r="A83" s="21">
+      <c r="A83" s="19">
         <v>74</v>
       </c>
-      <c r="B83" s="21">
+      <c r="B83" s="19">
         <v>3</v>
       </c>
-      <c r="C83" s="22">
+      <c r="C83" s="20">
         <v>0.06</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="15" thickBot="1">
-      <c r="A84" s="21">
+      <c r="A84" s="19">
         <v>75</v>
       </c>
-      <c r="B84" s="21">
+      <c r="B84" s="19">
         <v>5</v>
       </c>
-      <c r="C84" s="22">
+      <c r="C84" s="20">
         <v>0.1</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15" thickBot="1">
-      <c r="A85" s="21">
+      <c r="A85" s="19">
         <v>76</v>
       </c>
-      <c r="B85" s="21">
+      <c r="B85" s="19">
         <v>8</v>
       </c>
-      <c r="C85" s="22">
+      <c r="C85" s="20">
         <v>0.16</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="15" thickBot="1">
-      <c r="A86" s="21">
+      <c r="A86" s="19">
         <v>77</v>
       </c>
-      <c r="B86" s="21">
+      <c r="B86" s="19">
         <v>11</v>
       </c>
-      <c r="C86" s="22">
+      <c r="C86" s="20">
         <v>0.22</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="15" thickBot="1">
-      <c r="A87" s="21">
+      <c r="A87" s="19">
         <v>78</v>
       </c>
-      <c r="B87" s="21">
+      <c r="B87" s="19">
         <v>9</v>
       </c>
-      <c r="C87" s="22">
+      <c r="C87" s="20">
         <v>0.18</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="15" thickBot="1">
-      <c r="A88" s="21">
+      <c r="A88" s="19">
         <v>79</v>
       </c>
-      <c r="B88" s="21">
+      <c r="B88" s="19">
         <v>7</v>
       </c>
-      <c r="C88" s="22">
+      <c r="C88" s="20">
         <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="15" thickBot="1">
-      <c r="A89" s="21">
+      <c r="A89" s="19">
         <v>80</v>
       </c>
-      <c r="B89" s="21">
+      <c r="B89" s="19">
         <v>3</v>
       </c>
-      <c r="C89" s="22">
+      <c r="C89" s="20">
         <v>0.06</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="15" thickBot="1">
-      <c r="A90" s="21">
+      <c r="A90" s="19">
         <v>81</v>
       </c>
-      <c r="B90" s="21">
+      <c r="B90" s="19">
         <v>5</v>
       </c>
-      <c r="C90" s="22">
+      <c r="C90" s="20">
         <v>0.1</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="15" thickBot="1">
-      <c r="A91" s="21">
+      <c r="A91" s="19">
         <v>82</v>
       </c>
-      <c r="B91" s="21">
+      <c r="B91" s="19">
         <v>2</v>
       </c>
-      <c r="C91" s="22">
+      <c r="C91" s="20">
         <v>0.04</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="15" thickBot="1">
-      <c r="A92" s="21">
+      <c r="A92" s="19">
         <v>83</v>
       </c>
-      <c r="B92" s="21">
+      <c r="B92" s="19">
         <v>1</v>
       </c>
-      <c r="C92" s="22">
+      <c r="C92" s="20">
         <v>0.02</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="15" thickBot="1">
-      <c r="A93" s="21">
+      <c r="A93" s="19">
         <v>84</v>
       </c>
-      <c r="B93" s="21">
+      <c r="B93" s="19">
         <v>4</v>
       </c>
-      <c r="C93" s="22">
+      <c r="C93" s="20">
         <v>0.08</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="15" thickBot="1">
-      <c r="A94" s="21">
+      <c r="A94" s="19">
         <v>85</v>
       </c>
-      <c r="B94" s="21">
+      <c r="B94" s="19">
         <v>5</v>
       </c>
-      <c r="C94" s="22">
+      <c r="C94" s="20">
         <v>0.1</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="15" thickBot="1">
-      <c r="A95" s="21">
+      <c r="A95" s="19">
         <v>86</v>
       </c>
-      <c r="B95" s="21">
+      <c r="B95" s="19">
         <v>3</v>
       </c>
-      <c r="C95" s="22">
+      <c r="C95" s="20">
         <v>0.06</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="15" thickBot="1">
-      <c r="A96" s="21">
+      <c r="A96" s="19">
         <v>87</v>
       </c>
-      <c r="B96" s="21">
+      <c r="B96" s="19">
         <v>7</v>
       </c>
-      <c r="C96" s="22">
+      <c r="C96" s="20">
         <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="15" thickBot="1">
-      <c r="A97" s="21">
+      <c r="A97" s="19">
         <v>88</v>
       </c>
-      <c r="B97" s="21">
+      <c r="B97" s="19">
         <v>6</v>
       </c>
-      <c r="C97" s="22">
+      <c r="C97" s="20">
         <v>0.12</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="15" thickBot="1">
-      <c r="A98" s="21">
+      <c r="A98" s="19">
         <v>89</v>
       </c>
-      <c r="B98" s="21">
+      <c r="B98" s="19">
         <v>4</v>
       </c>
-      <c r="C98" s="22">
+      <c r="C98" s="20">
         <v>0.08</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="15" thickBot="1">
-      <c r="A99" s="21">
+      <c r="A99" s="19">
         <v>90</v>
       </c>
-      <c r="B99" s="21">
+      <c r="B99" s="19">
         <v>4</v>
       </c>
-      <c r="C99" s="22">
+      <c r="C99" s="20">
         <v>0.08</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="15" thickBot="1">
-      <c r="A100" s="21">
+      <c r="A100" s="19">
         <v>91</v>
       </c>
-      <c r="B100" s="21">
+      <c r="B100" s="19">
         <v>6</v>
       </c>
-      <c r="C100" s="22">
+      <c r="C100" s="20">
         <v>0.12</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="15" thickBot="1">
-      <c r="A101" s="21">
+      <c r="A101" s="19">
         <v>92</v>
       </c>
-      <c r="B101" s="21">
+      <c r="B101" s="19">
         <v>8</v>
       </c>
-      <c r="C101" s="22">
+      <c r="C101" s="20">
         <v>0.16</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="15" thickBot="1">
-      <c r="A102" s="21">
+      <c r="A102" s="19">
         <v>93</v>
       </c>
-      <c r="B102" s="21">
+      <c r="B102" s="19">
         <v>5</v>
       </c>
-      <c r="C102" s="22">
+      <c r="C102" s="20">
         <v>0.1</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="15" thickBot="1">
-      <c r="A103" s="21">
+      <c r="A103" s="19">
         <v>94</v>
       </c>
-      <c r="B103" s="21">
+      <c r="B103" s="19">
         <v>6</v>
       </c>
-      <c r="C103" s="22">
+      <c r="C103" s="20">
         <v>0.12</v>
       </c>
     </row>
@@ -13073,716 +13073,716 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="55.8" thickBot="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="24" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1">
-      <c r="A2" s="21">
+      <c r="A2" s="19">
         <v>1</v>
       </c>
-      <c r="B2" s="21">
+      <c r="B2" s="19">
         <v>100</v>
       </c>
-      <c r="C2" s="21">
+      <c r="C2" s="19">
         <v>12</v>
       </c>
-      <c r="D2" s="23">
+      <c r="D2" s="21">
         <f>C2/B2</f>
         <v>0.12</v>
       </c>
-      <c r="E2" s="25">
+      <c r="E2" s="23">
         <f>SQRT(($D$30*(1-$D$30)/B2))</f>
         <v>2.9352024271484114E-2</v>
       </c>
-      <c r="F2" s="25">
+      <c r="F2" s="23">
         <f>$D$30+(3*E2)</f>
         <v>0.18327728493566448</v>
       </c>
-      <c r="G2" s="25">
+      <c r="G2" s="23">
         <f>$D$30-(3*E2)</f>
         <v>7.165139306759799E-3</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" thickBot="1">
-      <c r="A3" s="21">
+      <c r="A3" s="19">
         <v>2</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="19">
         <v>80</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="19">
         <v>8</v>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="21">
         <f t="shared" ref="D3:D26" si="0">C3/B3</f>
         <v>0.1</v>
       </c>
-      <c r="E3" s="25">
+      <c r="E3" s="23">
         <f t="shared" ref="E3:E26" si="1">SQRT(($D$30*(1-$D$30)/B3))</f>
         <v>3.2816560774131108E-2</v>
       </c>
-      <c r="F3" s="25">
+      <c r="F3" s="23">
         <f t="shared" ref="F3:F26" si="2">$D$30+(3*E3)</f>
         <v>0.19367089444360547</v>
       </c>
-      <c r="G3" s="25">
+      <c r="G3" s="23">
         <f t="shared" ref="G3:G26" si="3">$D$30-(3*E3)</f>
         <v>-3.22847020118118E-3</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1">
-      <c r="A4" s="21">
+      <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="19">
         <v>80</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="19">
         <v>6</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="21">
         <f t="shared" si="0"/>
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="23">
         <f t="shared" si="1"/>
         <v>3.2816560774131108E-2</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="23">
         <f t="shared" si="2"/>
         <v>0.19367089444360547</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="23">
         <f t="shared" si="3"/>
         <v>-3.22847020118118E-3</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" thickBot="1">
-      <c r="A5" s="21">
+      <c r="A5" s="19">
         <v>4</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="19">
         <v>100</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="19">
         <v>9</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="21">
         <f t="shared" si="0"/>
         <v>0.09</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="23">
         <f t="shared" si="1"/>
         <v>2.9352024271484114E-2</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="23">
         <f t="shared" si="2"/>
         <v>0.18327728493566448</v>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="23">
         <f t="shared" si="3"/>
         <v>7.165139306759799E-3</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1">
-      <c r="A6" s="21">
+      <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="19">
         <v>110</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="19">
         <v>10</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="21">
         <f t="shared" si="0"/>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="23">
         <f t="shared" si="1"/>
         <v>2.7986057061488715E-2</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="23">
         <f t="shared" si="2"/>
         <v>0.17917938330567829</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="23">
         <f t="shared" si="3"/>
         <v>1.1263040936745988E-2</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1">
-      <c r="A7" s="21">
+      <c r="A7" s="19">
         <v>6</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="19">
         <v>110</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="19">
         <v>12</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="21">
         <f t="shared" si="0"/>
         <v>0.10909090909090909</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="23">
         <f t="shared" si="1"/>
         <v>2.7986057061488715E-2</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="23">
         <f t="shared" si="2"/>
         <v>0.17917938330567829</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="23">
         <f t="shared" si="3"/>
         <v>1.1263040936745988E-2</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" thickBot="1">
-      <c r="A8" s="21">
+      <c r="A8" s="19">
         <v>7</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="19">
         <v>100</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="19">
         <v>11</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="21">
         <f t="shared" si="0"/>
         <v>0.11</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="23">
         <f t="shared" si="1"/>
         <v>2.9352024271484114E-2</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="23">
         <f t="shared" si="2"/>
         <v>0.18327728493566448</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="23">
         <f t="shared" si="3"/>
         <v>7.165139306759799E-3</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1">
-      <c r="A9" s="21">
+      <c r="A9" s="19">
         <v>8</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="19">
         <v>100</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="19">
         <v>16</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="21">
         <f t="shared" si="0"/>
         <v>0.16</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="23">
         <f t="shared" si="1"/>
         <v>2.9352024271484114E-2</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="23">
         <f t="shared" si="2"/>
         <v>0.18327728493566448</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="23">
         <f t="shared" si="3"/>
         <v>7.165139306759799E-3</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1">
-      <c r="A10" s="21">
+      <c r="A10" s="19">
         <v>9</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="19">
         <v>90</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="19">
         <v>10</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="21">
         <f t="shared" si="0"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="23">
         <f t="shared" si="1"/>
         <v>3.0939750211478087E-2</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="23">
         <f t="shared" si="2"/>
         <v>0.1880404627556464</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="23">
         <f t="shared" si="3"/>
         <v>2.401961486777876E-3</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" thickBot="1">
-      <c r="A11" s="21">
+      <c r="A11" s="19">
         <v>10</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="19">
         <v>90</v>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="19">
         <v>6</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="21">
         <f t="shared" si="0"/>
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="23">
         <f t="shared" si="1"/>
         <v>3.0939750211478087E-2</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="23">
         <f t="shared" si="2"/>
         <v>0.1880404627556464</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="23">
         <f t="shared" si="3"/>
         <v>2.401961486777876E-3</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" thickBot="1">
-      <c r="A12" s="21">
+      <c r="A12" s="19">
         <v>11</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="19">
         <v>110</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="19">
         <v>20</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="21">
         <f t="shared" si="0"/>
         <v>0.18181818181818182</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="23">
         <f t="shared" si="1"/>
         <v>2.7986057061488715E-2</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="23">
         <f t="shared" si="2"/>
         <v>0.17917938330567829</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="23">
         <f t="shared" si="3"/>
         <v>1.1263040936745988E-2</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" thickBot="1">
-      <c r="A13" s="21">
+      <c r="A13" s="19">
         <v>12</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="19">
         <v>120</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="19">
         <v>15</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="21">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="23">
         <f t="shared" si="1"/>
         <v>2.6794609669884981E-2</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="23">
         <f t="shared" si="2"/>
         <v>0.17560504113086708</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="23">
         <f t="shared" si="3"/>
         <v>1.483738311155719E-2</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1">
-      <c r="A14" s="21">
+      <c r="A14" s="19">
         <v>13</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="19">
         <v>120</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="19">
         <v>9</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="21">
         <f t="shared" si="0"/>
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="23">
         <f t="shared" si="1"/>
         <v>2.6794609669884981E-2</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="23">
         <f t="shared" si="2"/>
         <v>0.17560504113086708</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="23">
         <f t="shared" si="3"/>
         <v>1.483738311155719E-2</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1">
-      <c r="A15" s="21">
+      <c r="A15" s="19">
         <v>14</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="19">
         <v>120</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="19">
         <v>8</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="21">
         <f t="shared" si="0"/>
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="23">
         <f t="shared" si="1"/>
         <v>2.6794609669884981E-2</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="23">
         <f t="shared" si="2"/>
         <v>0.17560504113086708</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="23">
         <f t="shared" si="3"/>
         <v>1.483738311155719E-2</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" thickBot="1">
-      <c r="A16" s="21">
+      <c r="A16" s="19">
         <v>15</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="19">
         <v>110</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="19">
         <v>6</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="21">
         <f t="shared" si="0"/>
         <v>5.4545454545454543E-2</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="23">
         <f t="shared" si="1"/>
         <v>2.7986057061488715E-2</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="23">
         <f t="shared" si="2"/>
         <v>0.17917938330567829</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="23">
         <f t="shared" si="3"/>
         <v>1.1263040936745988E-2</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1">
-      <c r="A17" s="21">
+      <c r="A17" s="19">
         <v>16</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="19">
         <v>80</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="19">
         <v>8</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="21">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="23">
         <f t="shared" si="1"/>
         <v>3.2816560774131108E-2</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="23">
         <f t="shared" si="2"/>
         <v>0.19367089444360547</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="23">
         <f t="shared" si="3"/>
         <v>-3.22847020118118E-3</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" thickBot="1">
-      <c r="A18" s="21">
+      <c r="A18" s="19">
         <v>17</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="19">
         <v>80</v>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="19">
         <v>10</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="21">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="23">
         <f t="shared" si="1"/>
         <v>3.2816560774131108E-2</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="23">
         <f t="shared" si="2"/>
         <v>0.19367089444360547</v>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="23">
         <f t="shared" si="3"/>
         <v>-3.22847020118118E-3</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" thickBot="1">
-      <c r="A19" s="21">
+      <c r="A19" s="19">
         <v>18</v>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="19">
         <v>80</v>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="19">
         <v>7</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="21">
         <f t="shared" si="0"/>
         <v>8.7499999999999994E-2</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="23">
         <f t="shared" si="1"/>
         <v>3.2816560774131108E-2</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="23">
         <f t="shared" si="2"/>
         <v>0.19367089444360547</v>
       </c>
-      <c r="G19" s="25">
+      <c r="G19" s="23">
         <f t="shared" si="3"/>
         <v>-3.22847020118118E-3</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" thickBot="1">
-      <c r="A20" s="21">
+      <c r="A20" s="19">
         <v>19</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="19">
         <v>90</v>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="19">
         <v>5</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="21">
         <f t="shared" si="0"/>
         <v>5.5555555555555552E-2</v>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="23">
         <f t="shared" si="1"/>
         <v>3.0939750211478087E-2</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="23">
         <f t="shared" si="2"/>
         <v>0.1880404627556464</v>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="23">
         <f t="shared" si="3"/>
         <v>2.401961486777876E-3</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" thickBot="1">
-      <c r="A21" s="21">
+      <c r="A21" s="19">
         <v>20</v>
       </c>
-      <c r="B21" s="21">
+      <c r="B21" s="19">
         <v>100</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="19">
         <v>8</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="21">
         <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="23">
         <f t="shared" si="1"/>
         <v>2.9352024271484114E-2</v>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="23">
         <f t="shared" si="2"/>
         <v>0.18327728493566448</v>
       </c>
-      <c r="G21" s="25">
+      <c r="G21" s="23">
         <f t="shared" si="3"/>
         <v>7.165139306759799E-3</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" thickBot="1">
-      <c r="A22" s="21">
+      <c r="A22" s="19">
         <v>21</v>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="19">
         <v>100</v>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="19">
         <v>5</v>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="21">
         <f t="shared" si="0"/>
         <v>0.05</v>
       </c>
-      <c r="E22" s="25">
+      <c r="E22" s="23">
         <f t="shared" si="1"/>
         <v>2.9352024271484114E-2</v>
       </c>
-      <c r="F22" s="25">
+      <c r="F22" s="23">
         <f t="shared" si="2"/>
         <v>0.18327728493566448</v>
       </c>
-      <c r="G22" s="25">
+      <c r="G22" s="23">
         <f t="shared" si="3"/>
         <v>7.165139306759799E-3</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" thickBot="1">
-      <c r="A23" s="21">
+      <c r="A23" s="19">
         <v>22</v>
       </c>
-      <c r="B23" s="21">
+      <c r="B23" s="19">
         <v>100</v>
       </c>
-      <c r="C23" s="21">
+      <c r="C23" s="19">
         <v>8</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="21">
         <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
-      <c r="E23" s="25">
+      <c r="E23" s="23">
         <f t="shared" si="1"/>
         <v>2.9352024271484114E-2</v>
       </c>
-      <c r="F23" s="25">
+      <c r="F23" s="23">
         <f t="shared" si="2"/>
         <v>0.18327728493566448</v>
       </c>
-      <c r="G23" s="25">
+      <c r="G23" s="23">
         <f t="shared" si="3"/>
         <v>7.165139306759799E-3</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" thickBot="1">
-      <c r="A24" s="21">
+      <c r="A24" s="19">
         <v>23</v>
       </c>
-      <c r="B24" s="21">
+      <c r="B24" s="19">
         <v>100</v>
       </c>
-      <c r="C24" s="21">
+      <c r="C24" s="19">
         <v>10</v>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="21">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
-      <c r="E24" s="25">
+      <c r="E24" s="23">
         <f t="shared" si="1"/>
         <v>2.9352024271484114E-2</v>
       </c>
-      <c r="F24" s="25">
+      <c r="F24" s="23">
         <f t="shared" si="2"/>
         <v>0.18327728493566448</v>
       </c>
-      <c r="G24" s="25">
+      <c r="G24" s="23">
         <f t="shared" si="3"/>
         <v>7.165139306759799E-3</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" thickBot="1">
-      <c r="A25" s="21">
+      <c r="A25" s="19">
         <v>24</v>
       </c>
-      <c r="B25" s="21">
+      <c r="B25" s="19">
         <v>90</v>
       </c>
-      <c r="C25" s="21">
+      <c r="C25" s="19">
         <v>6</v>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="21">
         <f t="shared" si="0"/>
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="E25" s="25">
+      <c r="E25" s="23">
         <f t="shared" si="1"/>
         <v>3.0939750211478087E-2</v>
       </c>
-      <c r="F25" s="25">
+      <c r="F25" s="23">
         <f t="shared" si="2"/>
         <v>0.1880404627556464</v>
       </c>
-      <c r="G25" s="25">
+      <c r="G25" s="23">
         <f t="shared" si="3"/>
         <v>2.401961486777876E-3</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" thickBot="1">
-      <c r="A26" s="21">
+      <c r="A26" s="19">
         <v>25</v>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="19">
         <v>90</v>
       </c>
-      <c r="C26" s="21">
+      <c r="C26" s="19">
         <v>9</v>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="21">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
-      <c r="E26" s="25">
+      <c r="E26" s="23">
         <f t="shared" si="1"/>
         <v>3.0939750211478087E-2</v>
       </c>
-      <c r="F26" s="25">
+      <c r="F26" s="23">
         <f t="shared" si="2"/>
         <v>0.1880404627556464</v>
       </c>
-      <c r="G26" s="25">
+      <c r="G26" s="23">
         <f t="shared" si="3"/>
         <v>2.401961486777876E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="42" thickBot="1">
-      <c r="A27" s="19" t="s">
+    <row r="27" spans="1:7" ht="15" thickBot="1">
+      <c r="A27" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="17">
         <f>SUM(B2:B26)</f>
         <v>2450</v>
       </c>
-      <c r="C27" s="19">
+      <c r="C27" s="17">
         <f>SUM(C2:C26)</f>
         <v>234</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="22">
         <f>SUM(D2:D26)</f>
         <v>2.3805303030303033</v>
       </c>
@@ -13793,13 +13793,13 @@
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="D30" s="25">
+      <c r="D30" s="23">
         <f>AVERAGE(D2:D26)</f>
         <v>9.5221212121212137E-2</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="D31" s="25">
+      <c r="D31" s="23">
         <f>1-D30</f>
         <v>0.90477878787878785</v>
       </c>
@@ -13817,219 +13817,219 @@
     <col min="1" max="2" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="42" thickBot="1">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:2" ht="28.2" thickBot="1">
+      <c r="A1" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="18" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" thickBot="1">
-      <c r="A2" s="21">
+      <c r="A2" s="19">
         <v>1</v>
       </c>
-      <c r="B2" s="22">
+      <c r="B2" s="20">
         <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" thickBot="1">
-      <c r="A3" s="21">
+      <c r="A3" s="19">
         <v>2</v>
       </c>
-      <c r="B3" s="22">
+      <c r="B3" s="20">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" thickBot="1">
-      <c r="A4" s="21">
+      <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4" s="22">
+      <c r="B4" s="20">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" thickBot="1">
-      <c r="A5" s="21">
+      <c r="A5" s="19">
         <v>4</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="20">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" thickBot="1">
-      <c r="A6" s="21">
+      <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="20">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" thickBot="1">
-      <c r="A7" s="21">
+      <c r="A7" s="19">
         <v>6</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="20">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" thickBot="1">
-      <c r="A8" s="21">
+      <c r="A8" s="19">
         <v>7</v>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="20">
         <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" thickBot="1">
-      <c r="A9" s="21">
+      <c r="A9" s="19">
         <v>8</v>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="20">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15" thickBot="1">
-      <c r="A10" s="21">
+      <c r="A10" s="19">
         <v>9</v>
       </c>
-      <c r="B10" s="22">
+      <c r="B10" s="20">
         <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15" thickBot="1">
-      <c r="A11" s="21">
+      <c r="A11" s="19">
         <v>10</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="20">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15" thickBot="1">
-      <c r="A12" s="21">
+      <c r="A12" s="19">
         <v>11</v>
       </c>
-      <c r="B12" s="22">
+      <c r="B12" s="20">
         <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15" thickBot="1">
-      <c r="A13" s="21">
+      <c r="A13" s="19">
         <v>12</v>
       </c>
-      <c r="B13" s="22">
+      <c r="B13" s="20">
         <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15" thickBot="1">
-      <c r="A14" s="21">
+      <c r="A14" s="19">
         <v>13</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="20">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15" thickBot="1">
-      <c r="A15" s="21">
+      <c r="A15" s="19">
         <v>14</v>
       </c>
-      <c r="B15" s="22">
+      <c r="B15" s="20">
         <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15" thickBot="1">
-      <c r="A16" s="21">
+      <c r="A16" s="19">
         <v>15</v>
       </c>
-      <c r="B16" s="22">
+      <c r="B16" s="20">
         <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15" thickBot="1">
-      <c r="A17" s="21">
+      <c r="A17" s="19">
         <v>16</v>
       </c>
-      <c r="B17" s="22">
+      <c r="B17" s="20">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15" thickBot="1">
-      <c r="A18" s="21">
+      <c r="A18" s="19">
         <v>17</v>
       </c>
-      <c r="B18" s="22">
+      <c r="B18" s="20">
         <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15" thickBot="1">
-      <c r="A19" s="21">
+      <c r="A19" s="19">
         <v>18</v>
       </c>
-      <c r="B19" s="22">
+      <c r="B19" s="20">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15" thickBot="1">
-      <c r="A20" s="21">
+      <c r="A20" s="19">
         <v>19</v>
       </c>
-      <c r="B20" s="22">
+      <c r="B20" s="20">
         <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15" thickBot="1">
-      <c r="A21" s="21">
+      <c r="A21" s="19">
         <v>20</v>
       </c>
-      <c r="B21" s="22">
+      <c r="B21" s="20">
         <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15" thickBot="1">
-      <c r="A22" s="21">
+      <c r="A22" s="19">
         <v>21</v>
       </c>
-      <c r="B22" s="22">
+      <c r="B22" s="20">
         <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15" thickBot="1">
-      <c r="A23" s="21">
+      <c r="A23" s="19">
         <v>22</v>
       </c>
-      <c r="B23" s="22">
+      <c r="B23" s="20">
         <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15" thickBot="1">
-      <c r="A24" s="21">
+      <c r="A24" s="19">
         <v>23</v>
       </c>
-      <c r="B24" s="22">
+      <c r="B24" s="20">
         <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15" thickBot="1">
-      <c r="A25" s="21">
+      <c r="A25" s="19">
         <v>24</v>
       </c>
-      <c r="B25" s="22">
+      <c r="B25" s="20">
         <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15" thickBot="1">
-      <c r="A26" s="21">
+      <c r="A26" s="19">
         <v>25</v>
       </c>
-      <c r="B26" s="22">
+      <c r="B26" s="20">
         <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15" thickBot="1">
-      <c r="A27" s="21">
+      <c r="A27" s="19">
         <v>26</v>
       </c>
-      <c r="B27" s="22">
+      <c r="B27" s="20">
         <v>15</v>
       </c>
     </row>
@@ -14047,674 +14047,674 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" thickBot="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="24" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1">
-      <c r="A2" s="21">
+      <c r="A2" s="19">
         <v>1</v>
       </c>
-      <c r="B2" s="21">
+      <c r="B2" s="19">
         <v>100</v>
       </c>
-      <c r="C2" s="21">
+      <c r="C2" s="19">
         <v>18</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="20">
         <v>0.18</v>
       </c>
       <c r="E2">
         <f>SQRT($D$27/B2)</f>
         <v>4.4181444068749041E-2</v>
       </c>
-      <c r="F2" s="25">
+      <c r="F2" s="23">
         <f>$D$27+(3*E2)</f>
         <v>0.3277443322062471</v>
       </c>
-      <c r="G2" s="25">
+      <c r="G2" s="23">
         <f>$D$27-(3*E2)</f>
         <v>6.2655667793752867E-2</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" thickBot="1">
-      <c r="A3" s="21">
+      <c r="A3" s="19">
         <v>2</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="19">
         <v>100</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="19">
         <v>22</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="20">
         <v>0.22</v>
       </c>
       <c r="E3">
         <f t="shared" ref="E3:E26" si="0">SQRT($D$27/B3)</f>
         <v>4.4181444068749041E-2</v>
       </c>
-      <c r="F3" s="25">
+      <c r="F3" s="23">
         <f t="shared" ref="F3:F26" si="1">$D$27+(3*E3)</f>
         <v>0.3277443322062471</v>
       </c>
-      <c r="G3" s="25">
+      <c r="G3" s="23">
         <f t="shared" ref="G3:G26" si="2">$D$27-(3*E3)</f>
         <v>6.2655667793752867E-2</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1">
-      <c r="A4" s="21">
+      <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="19">
         <v>90</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="19">
         <v>15</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="20">
         <v>0.17</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
         <v>4.6571331190861279E-2</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="23">
         <f t="shared" si="1"/>
         <v>0.33491399357258383</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="23">
         <f t="shared" si="2"/>
         <v>5.5486006427416135E-2</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" thickBot="1">
-      <c r="A5" s="21">
+      <c r="A5" s="19">
         <v>4</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="19">
         <v>110</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="19">
         <v>25</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="20">
         <v>0.23</v>
       </c>
       <c r="E5">
         <f t="shared" si="0"/>
         <v>4.2125354058398776E-2</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="23">
         <f t="shared" si="1"/>
         <v>0.3215760621751963</v>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="23">
         <f t="shared" si="2"/>
         <v>6.8823937824803672E-2</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1">
-      <c r="A6" s="21">
+      <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="19">
         <v>100</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="19">
         <v>12</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="20">
         <v>0.12</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
         <v>4.4181444068749041E-2</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="23">
         <f t="shared" si="1"/>
         <v>0.3277443322062471</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="23">
         <f t="shared" si="2"/>
         <v>6.2655667793752867E-2</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1">
-      <c r="A7" s="21">
+      <c r="A7" s="19">
         <v>6</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="19">
         <v>100</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="19">
         <v>19</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="20">
         <v>0.19</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
         <v>4.4181444068749041E-2</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="23">
         <f t="shared" si="1"/>
         <v>0.3277443322062471</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="23">
         <f t="shared" si="2"/>
         <v>6.2655667793752867E-2</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" thickBot="1">
-      <c r="A8" s="21">
+      <c r="A8" s="19">
         <v>7</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="19">
         <v>95</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="19">
         <v>20</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="20">
         <v>0.21</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
         <v>4.5329205178397544E-2</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="23">
         <f t="shared" si="1"/>
         <v>0.3311876155351926</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="23">
         <f t="shared" si="2"/>
         <v>5.9212384464807366E-2</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1">
-      <c r="A9" s="21">
+      <c r="A9" s="19">
         <v>8</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="19">
         <v>105</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="19">
         <v>24</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="20">
         <v>0.23</v>
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
         <v>4.3116674489663727E-2</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="23">
         <f t="shared" si="1"/>
         <v>0.3245500234689912</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="23">
         <f t="shared" si="2"/>
         <v>6.5849976531008797E-2</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1">
-      <c r="A10" s="21">
+      <c r="A10" s="19">
         <v>9</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="19">
         <v>100</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="19">
         <v>30</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="20">
         <v>0.3</v>
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
         <v>4.4181444068749041E-2</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="23">
         <f t="shared" si="1"/>
         <v>0.3277443322062471</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="23">
         <f t="shared" si="2"/>
         <v>6.2655667793752867E-2</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" thickBot="1">
-      <c r="A11" s="21">
+      <c r="A11" s="19">
         <v>10</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="19">
         <v>100</v>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="19">
         <v>17</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="20">
         <v>0.17</v>
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
         <v>4.4181444068749041E-2</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="23">
         <f t="shared" si="1"/>
         <v>0.3277443322062471</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="23">
         <f t="shared" si="2"/>
         <v>6.2655667793752867E-2</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" thickBot="1">
-      <c r="A12" s="21">
+      <c r="A12" s="19">
         <v>11</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="19">
         <v>90</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="19">
         <v>14</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="20">
         <v>0.16</v>
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
         <v>4.6571331190861279E-2</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="23">
         <f t="shared" si="1"/>
         <v>0.33491399357258383</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="23">
         <f t="shared" si="2"/>
         <v>5.5486006427416135E-2</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" thickBot="1">
-      <c r="A13" s="21">
+      <c r="A13" s="19">
         <v>12</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="19">
         <v>110</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="19">
         <v>22</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="20">
         <v>0.2</v>
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
         <v>4.2125354058398776E-2</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="23">
         <f t="shared" si="1"/>
         <v>0.3215760621751963</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="23">
         <f t="shared" si="2"/>
         <v>6.8823937824803672E-2</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1">
-      <c r="A14" s="21">
+      <c r="A14" s="19">
         <v>13</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="19">
         <v>100</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="19">
         <v>16</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="20">
         <v>0.16</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
         <v>4.4181444068749041E-2</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="23">
         <f t="shared" si="1"/>
         <v>0.3277443322062471</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="23">
         <f t="shared" si="2"/>
         <v>6.2655667793752867E-2</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1">
-      <c r="A15" s="21">
+      <c r="A15" s="19">
         <v>14</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="19">
         <v>100</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="19">
         <v>21</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="20">
         <v>0.21</v>
       </c>
       <c r="E15">
         <f t="shared" si="0"/>
         <v>4.4181444068749041E-2</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="23">
         <f t="shared" si="1"/>
         <v>0.3277443322062471</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="23">
         <f t="shared" si="2"/>
         <v>6.2655667793752867E-2</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" thickBot="1">
-      <c r="A16" s="21">
+      <c r="A16" s="19">
         <v>15</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="19">
         <v>95</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="19">
         <v>18</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="20">
         <v>0.19</v>
       </c>
       <c r="E16">
         <f t="shared" si="0"/>
         <v>4.5329205178397544E-2</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="23">
         <f t="shared" si="1"/>
         <v>0.3311876155351926</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="23">
         <f t="shared" si="2"/>
         <v>5.9212384464807366E-2</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1">
-      <c r="A17" s="21">
+      <c r="A17" s="19">
         <v>16</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="19">
         <v>105</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="19">
         <v>26</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="20">
         <v>0.25</v>
       </c>
       <c r="E17">
         <f t="shared" si="0"/>
         <v>4.3116674489663727E-2</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="23">
         <f t="shared" si="1"/>
         <v>0.3245500234689912</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="23">
         <f t="shared" si="2"/>
         <v>6.5849976531008797E-2</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" thickBot="1">
-      <c r="A18" s="21">
+      <c r="A18" s="19">
         <v>17</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="19">
         <v>100</v>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="19">
         <v>19</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="20">
         <v>0.19</v>
       </c>
       <c r="E18">
         <f t="shared" si="0"/>
         <v>4.4181444068749041E-2</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="23">
         <f t="shared" si="1"/>
         <v>0.3277443322062471</v>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="23">
         <f t="shared" si="2"/>
         <v>6.2655667793752867E-2</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" thickBot="1">
-      <c r="A19" s="21">
+      <c r="A19" s="19">
         <v>18</v>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="19">
         <v>100</v>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="19">
         <v>13</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="20">
         <v>0.13</v>
       </c>
       <c r="E19">
         <f t="shared" si="0"/>
         <v>4.4181444068749041E-2</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="23">
         <f t="shared" si="1"/>
         <v>0.3277443322062471</v>
       </c>
-      <c r="G19" s="25">
+      <c r="G19" s="23">
         <f t="shared" si="2"/>
         <v>6.2655667793752867E-2</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" thickBot="1">
-      <c r="A20" s="21">
+      <c r="A20" s="19">
         <v>19</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="19">
         <v>90</v>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="19">
         <v>12</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="20">
         <v>0.13</v>
       </c>
       <c r="E20">
         <f t="shared" si="0"/>
         <v>4.6571331190861279E-2</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="23">
         <f t="shared" si="1"/>
         <v>0.33491399357258383</v>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="23">
         <f t="shared" si="2"/>
         <v>5.5486006427416135E-2</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" thickBot="1">
-      <c r="A21" s="21">
+      <c r="A21" s="19">
         <v>20</v>
       </c>
-      <c r="B21" s="21">
+      <c r="B21" s="19">
         <v>110</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="19">
         <v>35</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="20">
         <v>0.32</v>
       </c>
       <c r="E21">
         <f t="shared" si="0"/>
         <v>4.2125354058398776E-2</v>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="23">
         <f t="shared" si="1"/>
         <v>0.3215760621751963</v>
       </c>
-      <c r="G21" s="25">
+      <c r="G21" s="23">
         <f t="shared" si="2"/>
         <v>6.8823937824803672E-2</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" thickBot="1">
-      <c r="A22" s="21">
+      <c r="A22" s="19">
         <v>21</v>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="19">
         <v>100</v>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="19">
         <v>20</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="20">
         <v>0.2</v>
       </c>
       <c r="E22">
         <f t="shared" si="0"/>
         <v>4.4181444068749041E-2</v>
       </c>
-      <c r="F22" s="25">
+      <c r="F22" s="23">
         <f t="shared" si="1"/>
         <v>0.3277443322062471</v>
       </c>
-      <c r="G22" s="25">
+      <c r="G22" s="23">
         <f t="shared" si="2"/>
         <v>6.2655667793752867E-2</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" thickBot="1">
-      <c r="A23" s="21">
+      <c r="A23" s="19">
         <v>22</v>
       </c>
-      <c r="B23" s="21">
+      <c r="B23" s="19">
         <v>100</v>
       </c>
-      <c r="C23" s="21">
+      <c r="C23" s="19">
         <v>18</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="20">
         <v>0.18</v>
       </c>
       <c r="E23">
         <f t="shared" si="0"/>
         <v>4.4181444068749041E-2</v>
       </c>
-      <c r="F23" s="25">
+      <c r="F23" s="23">
         <f t="shared" si="1"/>
         <v>0.3277443322062471</v>
       </c>
-      <c r="G23" s="25">
+      <c r="G23" s="23">
         <f t="shared" si="2"/>
         <v>6.2655667793752867E-2</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" thickBot="1">
-      <c r="A24" s="21">
+      <c r="A24" s="19">
         <v>23</v>
       </c>
-      <c r="B24" s="21">
+      <c r="B24" s="19">
         <v>95</v>
       </c>
-      <c r="C24" s="21">
+      <c r="C24" s="19">
         <v>15</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="20">
         <v>0.16</v>
       </c>
       <c r="E24">
         <f t="shared" si="0"/>
         <v>4.5329205178397544E-2</v>
       </c>
-      <c r="F24" s="25">
+      <c r="F24" s="23">
         <f t="shared" si="1"/>
         <v>0.3311876155351926</v>
       </c>
-      <c r="G24" s="25">
+      <c r="G24" s="23">
         <f t="shared" si="2"/>
         <v>5.9212384464807366E-2</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" thickBot="1">
-      <c r="A25" s="21">
+      <c r="A25" s="19">
         <v>24</v>
       </c>
-      <c r="B25" s="21">
+      <c r="B25" s="19">
         <v>105</v>
       </c>
-      <c r="C25" s="21">
+      <c r="C25" s="19">
         <v>22</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="20">
         <v>0.21</v>
       </c>
       <c r="E25">
         <f t="shared" si="0"/>
         <v>4.3116674489663727E-2</v>
       </c>
-      <c r="F25" s="25">
+      <c r="F25" s="23">
         <f t="shared" si="1"/>
         <v>0.3245500234689912</v>
       </c>
-      <c r="G25" s="25">
+      <c r="G25" s="23">
         <f t="shared" si="2"/>
         <v>6.5849976531008797E-2</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" thickBot="1">
-      <c r="A26" s="21">
+      <c r="A26" s="19">
         <v>25</v>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="19">
         <v>100</v>
       </c>
-      <c r="C26" s="21">
+      <c r="C26" s="19">
         <v>17</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="20">
         <v>0.17</v>
       </c>
       <c r="E26">
         <f t="shared" si="0"/>
         <v>4.4181444068749041E-2</v>
       </c>
-      <c r="F26" s="25">
+      <c r="F26" s="23">
         <f t="shared" si="1"/>
         <v>0.3277443322062471</v>
       </c>
-      <c r="G26" s="25">
+      <c r="G26" s="23">
         <f t="shared" si="2"/>
         <v>6.2655667793752867E-2</v>
       </c>
